--- a/malvern-cafes.xlsx
+++ b/malvern-cafes.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:R31"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -406,7 +406,18 @@
     <col min="4" max="4" width="9.83203125" customWidth="1"/>
     <col min="5" max="5" width="39.83203125" customWidth="1"/>
     <col min="6" max="6" width="100.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="69.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="100.83203125" customWidth="1"/>
+    <col min="10" max="10" width="100.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" customWidth="1"/>
+    <col min="13" max="13" width="13.83203125" customWidth="1"/>
+    <col min="14" max="14" width="39.83203125" customWidth="1"/>
+    <col min="15" max="15" width="98.83203125" customWidth="1"/>
+    <col min="16" max="16" width="29.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -429,6 +440,39 @@
         <v>Listing Link</v>
       </c>
       <c r="G1" t="str">
+        <v>Full Address</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Website</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Google Maps URL</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Detailed Rating</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Total Reviews</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Price Range</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Plus Code</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Check-in Time</v>
+      </c>
+      <c r="R1" t="str">
         <v>Extracted At</v>
       </c>
     </row>
@@ -452,7 +496,40 @@
         <v>https://www.google.com/maps/place/High+Society/data=!4m7!3m6!1s0x6ad669de84ea1b2f:0xdab68fcd9a2b0276!8m2!3d-37.8560263!4d145.0239643!16s%2Fg%2F11cjj62kzc!19sChIJLxvqhN5p1moRdgIrms2Ptto?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G2" t="str">
-        <v>3/9/2026, 5:58:55 PM</v>
+        <v>1102 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H2" t="str">
+        <v>+61 3 8578 4602</v>
+      </c>
+      <c r="I2" t="str">
+        <v>https://www.highsocietyarmadale.com/</v>
+      </c>
+      <c r="J2" t="str">
+        <v>https://www.google.com/maps/place/High+Society/@-37.8560263,145.0239643,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de84ea1b2f:0xdab68fcd9a2b0276!8m2!3d-37.8560263!4d145.0239643!16s%2Fg%2F11cjj62kzc?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K2" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N2" t="str">
+        <v>42VF+HH Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v>3/9/2026, 6:24:11 PM</v>
       </c>
     </row>
     <row r="3">
@@ -460,22 +537,55 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Mammoth Cafe Armadale</v>
+        <v>Small Wins (Previously Nine Yards)</v>
       </c>
       <c r="C3" t="str">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="D3" t="str">
-        <v>648</v>
+        <v>326</v>
       </c>
       <c r="E3" t="str">
         <v>$20–40</v>
       </c>
       <c r="F3" t="str">
-        <v>https://www.google.com/maps/place/Mammoth+Cafe+Armadale/data=!4m7!3m6!1s0x6ad669d64986365d:0xd89d1592f5b895c1!8m2!3d-37.849539!4d145.013157!16s%2Fg%2F11bw51sknh!19sChIJXTaGSdZp1moRwZW49ZIVndg?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Small+Wins+%28Previously+Nine+Yards%29/data=!4m7!3m6!1s0x6ad669c45f8dcb1f:0xd734227b45981edc!8m2!3d-37.8562109!4d145.0278178!16s%2Fg%2F11kzvgcx5_!19sChIJH8uNX8Rp1moR3B6YRXsiNNc?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G3" t="str">
-        <v>3/9/2026, 5:59:05 PM</v>
+        <v>1203 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H3" t="str">
+        <v>+61 3 9822 2014</v>
+      </c>
+      <c r="I3" t="str">
+        <v>https://linktr.ee/smallwins.armadale?utm_source=linktree_profile_share&amp;ltsid=637f127c-3936-408c-bdcb-1fa168d731d3</v>
+      </c>
+      <c r="J3" t="str">
+        <v>https://www.google.com/maps/place/Small+Wins+(Previously+Nine+Yards)/@-37.8562109,145.0278178,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669c45f8dcb1f:0xd734227b45981edc!8m2!3d-37.8562109!4d145.0278178!16s%2Fg%2F11kzvgcx5_?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K3" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N3" t="str">
+        <v>42VH+G4 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>3/9/2026, 6:24:20 PM</v>
       </c>
     </row>
     <row r="4">
@@ -483,22 +593,55 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Small Wins (Previously Nine Yards)</v>
+        <v>Mammoth Cafe Armadale</v>
       </c>
       <c r="C4" t="str">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="D4" t="str">
-        <v>326</v>
+        <v>648</v>
       </c>
       <c r="E4" t="str">
         <v>$20–40</v>
       </c>
       <c r="F4" t="str">
-        <v>https://www.google.com/maps/place/Small+Wins+%28Previously+Nine+Yards%29/data=!4m7!3m6!1s0x6ad669c45f8dcb1f:0xd734227b45981edc!8m2!3d-37.8562109!4d145.0278178!16s%2Fg%2F11kzvgcx5_!19sChIJH8uNX8Rp1moR3B6YRXsiNNc?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Mammoth+Cafe+Armadale/data=!4m7!3m6!1s0x6ad669d64986365d:0xd89d1592f5b895c1!8m2!3d-37.849539!4d145.013157!16s%2Fg%2F11bw51sknh!19sChIJXTaGSdZp1moRwZW49ZIVndg?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G4" t="str">
-        <v>3/9/2026, 5:59:17 PM</v>
+        <v>736 Malvern Rd, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H4" t="str">
+        <v>+61 3 9824 5239</v>
+      </c>
+      <c r="I4" t="str">
+        <v>https://mammotharmadale.com.au/</v>
+      </c>
+      <c r="J4" t="str">
+        <v>https://www.google.com/maps/place/Mammoth+Cafe+Armadale/@-37.849539,145.013157,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d64986365d:0xd89d1592f5b895c1!8m2!3d-37.849539!4d145.013157!16s%2Fg%2F11bw51sknh?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K4" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N4" t="str">
+        <v>5227+57 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>3/9/2026, 6:24:31 PM</v>
       </c>
     </row>
     <row r="5">
@@ -521,7 +664,40 @@
         <v>https://www.google.com/maps/place/Coffee+Ministry+Armadale/data=!4m7!3m6!1s0x6ad669432bb51f17:0xea4d193a38f79d53!8m2!3d-37.8567013!4d145.0186063!16s%2Fg%2F11vz35bn0y!19sChIJFx-1K0Np1moRU533ODoZTeo?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G5" t="str">
-        <v>3/9/2026, 5:59:27 PM</v>
+        <v>59A Armadale St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H5" t="str">
+        <v>+61 478 895 749</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>https://www.google.com/maps/place/Coffee+Ministry+Armadale/@-37.8567013,145.0186063,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669432bb51f17:0xea4d193a38f79d53!8m2!3d-37.8567013!4d145.0186063!16s%2Fg%2F11vz35bn0y?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K5" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="N5" t="str">
+        <v>42V9+8C Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>3/9/2026, 6:24:41 PM</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +720,40 @@
         <v>https://www.google.com/maps/place/Nigel/data=!4m7!3m6!1s0x6ad669626445af73:0xbeab4aab55e5322e!8m2!3d-37.856745!4d145.028871!16s%2Fg%2F11r9vw8v_v!19sChIJc69FZGJp1moRLjLlVatKq74?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G6" t="str">
-        <v>3/9/2026, 5:59:38 PM</v>
+        <v>1268 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H6" t="str">
+        <v>+61 3 8678 4080</v>
+      </c>
+      <c r="I6" t="str">
+        <v>https://www.nigelcoffee.com.au/</v>
+      </c>
+      <c r="J6" t="str">
+        <v>https://www.google.com/maps/place/Nigel/@-37.856745,145.028871,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669626445af73:0xbeab4aab55e5322e!8m2!3d-37.856745!4d145.028871!16s%2Fg%2F11r9vw8v_v?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K6" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="N6" t="str">
+        <v>42VH+8G Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v>3/9/2026, 6:24:53 PM</v>
       </c>
     </row>
     <row r="7">
@@ -567,7 +776,40 @@
         <v>https://www.google.com/maps/place/Moby/data=!4m7!3m6!1s0x6ad669de6f13bb59:0x4e6febc121ab688b!8m2!3d-37.8562195!4d145.0255233!16s%2Fg%2F11c2jv76j3!19sChIJWbsTb95p1moRi2irIcHrb04?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G7" t="str">
-        <v>3/9/2026, 5:59:48 PM</v>
+        <v>1150 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H7" t="str">
+        <v>+61 3 9509 2710</v>
+      </c>
+      <c r="I7" t="str">
+        <v>http://www.moby3143.com.au/</v>
+      </c>
+      <c r="J7" t="str">
+        <v>https://www.google.com/maps/place/Moby/@-37.8562195,145.0255233,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de6f13bb59:0x4e6febc121ab688b!8m2!3d-37.8562195!4d145.0255233!16s%2Fg%2F11c2jv76j3?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K7" t="str">
+        <v>4.1</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N7" t="str">
+        <v>42VG+G6 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v>3/9/2026, 6:25:03 PM</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +832,40 @@
         <v>https://www.google.com/maps/place/Bruno%26Co/data=!4m7!3m6!1s0x6ad669d959c2b787:0x4295029db5ebfd16!8m2!3d-37.8553894!4d145.0210376!16s%2Fg%2F11g8nzfvc0!19sChIJh7fCWdlp1moRFv3rtZ0ClUI?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G8" t="str">
-        <v>3/9/2026, 6:00:01 PM</v>
+        <v>1007 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H8" t="str">
+        <v>+61 3 9822 8515</v>
+      </c>
+      <c r="I8" t="str">
+        <v>https://brunoandco.com/</v>
+      </c>
+      <c r="J8" t="str">
+        <v>https://www.google.com/maps/place/Bruno%26Co/@-37.8553894,145.0210376,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d959c2b787:0x4295029db5ebfd16!8m2!3d-37.8553894!4d145.0210376!16s%2Fg%2F11g8nzfvc0?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K8" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N8" t="str">
+        <v>42VC+RC Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v>3/9/2026, 6:25:16 PM</v>
       </c>
     </row>
     <row r="9">
@@ -598,22 +873,55 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Cubbyhouse Canteen</v>
+        <v>Coin Laundry Cafe</v>
       </c>
       <c r="C9" t="str">
         <v>4.4</v>
       </c>
       <c r="D9" t="str">
-        <v>139</v>
+        <v>473</v>
       </c>
       <c r="E9" t="str">
-        <v>$1–20</v>
+        <v>$20–40</v>
       </c>
       <c r="F9" t="str">
-        <v>https://www.google.com/maps/place/Cubbyhouse+Canteen/data=!4m7!3m6!1s0x6ad669dcf5747179:0xdf909f92969a2708!8m2!3d-37.8583368!4d145.0234773!16s%2Fg%2F12qgl7jmj!19sChIJeXF09dxp1moRCCealpKfkN8?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Coin+Laundry+Cafe/data=!4m7!3m6!1s0x6ad669da5253ec73:0xf5f9f549eed96d7!8m2!3d-37.856665!4d145.0186204!16s%2Fg%2F1tgw5509!19sChIJc-xTUtpp1moR15btnlSfXw8?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G9" t="str">
-        <v>3/9/2026, 6:00:10 PM</v>
+        <v>61 Armadale St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H9" t="str">
+        <v>+61 3 9500 1888</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v>https://www.google.com/maps/place/Coin+Laundry+Cafe/@-37.856665,145.0186204,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669da5253ec73:0xf5f9f549eed96d7!8m2!3d-37.856665!4d145.0186204!16s%2Fg%2F1tgw5509?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K9" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N9" t="str">
+        <v>42V9+8C Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Bustling coffeehouse in a refurbished laundromat, serving inventive breakfast and lunch dishes.</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v>3/9/2026, 6:25:27 PM</v>
       </c>
     </row>
     <row r="10">
@@ -621,22 +929,55 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Coin Laundry Cafe</v>
+        <v>Pique Nique</v>
       </c>
       <c r="C10" t="str">
         <v>4.4</v>
       </c>
       <c r="D10" t="str">
-        <v>473</v>
+        <v>186</v>
       </c>
       <c r="E10" t="str">
         <v>$20–40</v>
       </c>
       <c r="F10" t="str">
-        <v>https://www.google.com/maps/place/Coin+Laundry+Cafe/data=!4m7!3m6!1s0x6ad669da5253ec73:0xf5f9f549eed96d7!8m2!3d-37.856665!4d145.0186204!16s%2Fg%2F1tgw5509!19sChIJc-xTUtpp1moR15btnlSfXw8?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Pique+Nique/data=!4m7!3m6!1s0x6ad669dc8a3b11fd:0x5c78c291e96d657!8m2!3d-37.8586088!4d145.0228889!16s%2Fg%2F1pzrk8chz!19sChIJ_RE7itxp1moRV9aWHimMxwU?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G10" t="str">
-        <v>3/9/2026, 6:00:22 PM</v>
+        <v>43 Union St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H10" t="str">
+        <v>+61 412 943 999</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>https://www.google.com/maps/place/Pique+Nique/@-37.8586088,145.0228889,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669dc8a3b11fd:0x5c78c291e96d657!8m2!3d-37.8586088!4d145.0228889!16s%2Fg%2F1pzrk8chz?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K10" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N10" t="str">
+        <v>42RF+H5 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v>3/9/2026, 6:25:36 PM</v>
       </c>
     </row>
     <row r="11">
@@ -644,22 +985,55 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Pique Nique</v>
+        <v>Cubbyhouse Canteen</v>
       </c>
       <c r="C11" t="str">
         <v>4.4</v>
       </c>
       <c r="D11" t="str">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="E11" t="str">
-        <v>$20–40</v>
+        <v>$1–20</v>
       </c>
       <c r="F11" t="str">
-        <v>https://www.google.com/maps/place/Pique+Nique/data=!4m7!3m6!1s0x6ad669dc8a3b11fd:0x5c78c291e96d657!8m2!3d-37.8586088!4d145.0228889!16s%2Fg%2F1pzrk8chz!19sChIJ_RE7itxp1moRV9aWHimMxwU?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Cubbyhouse+Canteen/data=!4m7!3m6!1s0x6ad669dcf5747179:0xdf909f92969a2708!8m2!3d-37.8583368!4d145.0234773!16s%2Fg%2F12qgl7jmj!19sChIJeXF09dxp1moRCCealpKfkN8?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G11" t="str">
-        <v>3/9/2026, 6:00:31 PM</v>
+        <v>43A Union St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H11" t="str">
+        <v>+61 421 173 886</v>
+      </c>
+      <c r="I11" t="str">
+        <v>https://www.cubbyhousecanteen.com.au/</v>
+      </c>
+      <c r="J11" t="str">
+        <v>https://www.google.com/maps/place/Cubbyhouse+Canteen/@-37.8583368,145.0234773,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669dcf5747179:0xdf909f92969a2708!8m2!3d-37.8583368!4d145.0234773!16s%2Fg%2F12qgl7jmj?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K11" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="N11" t="str">
+        <v>42RF+M9 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v>3/9/2026, 6:25:48 PM</v>
       </c>
     </row>
     <row r="12">
@@ -682,7 +1056,40 @@
         <v>https://www.google.com/maps/place/Saki%E2%80%99s+Coffee/data=!4m7!3m6!1s0x6ad6690f11b0c8c1:0xb507a9612c40a157!8m2!3d-37.8507822!4d145.0145116!16s%2Fg%2F11j4ksw4d1!19sChIJwciwEQ9p1moRV6FALGGpB7U?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G12" t="str">
-        <v>3/9/2026, 6:00:41 PM</v>
+        <v>1B Rose St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H12" t="str">
+        <v>+61 478 366 688</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>https://www.google.com/maps/place/Saki%E2%80%99s+Coffee/@-37.8507822,145.0145116,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6690f11b0c8c1:0xb507a9612c40a157!8m2!3d-37.8507822!4d145.0145116!16s%2Fg%2F11j4ksw4d1?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K12" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="N12" t="str">
+        <v>42X7+MR Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v>3/9/2026, 6:26:00 PM</v>
       </c>
     </row>
     <row r="13">
@@ -705,7 +1112,40 @@
         <v>https://www.google.com/maps/place/Ned%27s+Bake+%26+Bistro+Armadale/data=!4m7!3m6!1s0x6ad66948027c88b1:0x7666dc368074c0e!8m2!3d-37.855286!4d145.020309!16s%2Fg%2F11rv37b_d2!19sChIJsYh8Akhp1moRDkwHaMNtZgc?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G13" t="str">
-        <v>3/9/2026, 6:00:51 PM</v>
+        <v>963 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H13" t="str">
+        <v>+61 3 9824 4053</v>
+      </c>
+      <c r="I13" t="str">
+        <v>http://www.nedsbake.com.au/</v>
+      </c>
+      <c r="J13" t="str">
+        <v>https://www.google.com/maps/place/Ned's+Bake+%26+Bistro+Armadale/@-37.855286,145.020309,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad66948027c88b1:0x7666dc368074c0e!8m2!3d-37.855286!4d145.020309!16s%2Fg%2F11rv37b_d2?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K13" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N13" t="str">
+        <v>42VC+V4 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v>3/9/2026, 6:26:11 PM</v>
       </c>
     </row>
     <row r="14">
@@ -728,7 +1168,40 @@
         <v>https://www.google.com/maps/place/Hank%27s+Bagelry+-+Armadale/data=!4m7!3m6!1s0x6ad6692801c6214b:0xd7e38ffd0d1d64e6!8m2!3d-37.8507213!4d145.0142979!16s%2Fg%2F11scg38mxg!19sChIJSyHGAShp1moR5mQdDf2P49c?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G14" t="str">
-        <v>3/9/2026, 6:01:01 PM</v>
+        <v>13 Beatty Ave, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H14" t="str">
+        <v>+61 3 9125 1606</v>
+      </c>
+      <c r="I14" t="str">
+        <v>http://hanksbagelry.com.au/</v>
+      </c>
+      <c r="J14" t="str">
+        <v>https://www.google.com/maps/place/Hank's+Bagelry+-+Armadale/@-37.8507213,145.0142979,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6692801c6214b:0xd7e38ffd0d1d64e6!8m2!3d-37.8507213!4d145.0142979!16s%2Fg%2F11scg38mxg?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K14" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="N14" t="str">
+        <v>42X7+PP Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v>3/9/2026, 6:26:24 PM</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +1224,40 @@
         <v>https://www.google.com/maps/place/Lune+Croissanterie+Armadale/data=!4m7!3m6!1s0x6ad6693f828b403b:0xdd00a2c9456a6862!8m2!3d-37.8546269!4d145.0153947!16s%2Fg%2F11s57f8t2l!19sChIJO0CLgj9p1moRYmhqRcmiAN0?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G15" t="str">
-        <v>3/9/2026, 6:01:12 PM</v>
+        <v>835 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>https://www.lunecroissanterie.com/</v>
+      </c>
+      <c r="J15" t="str">
+        <v>https://www.google.com/maps/place/Lune+Croissanterie+Armadale/@-37.8546269,145.0153947,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6693f828b403b:0xdd00a2c9456a6862!8m2!3d-37.8546269!4d145.0153947!16s%2Fg%2F11s57f8t2l?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K15" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N15" t="str">
+        <v>42W8+45 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v>hello@lunecroissanterie.com</v>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v>3/9/2026, 6:26:33 PM</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +1280,40 @@
         <v>https://www.google.com/maps/place/Euro+Patisserie/data=!4m7!3m6!1s0x6ad669dbde7cc6fb:0x3d7ede4e124dd153!8m2!3d-37.8555027!4d145.0202229!16s%2Fg%2F1tghpqv0!19sChIJ-8Z83ttp1moRU9FNEk7efj0?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G16" t="str">
-        <v>3/9/2026, 6:01:23 PM</v>
+        <v>974 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H16" t="str">
+        <v>+61 3 9509 5166</v>
+      </c>
+      <c r="I16" t="str">
+        <v>https://patisseries.com.au/</v>
+      </c>
+      <c r="J16" t="str">
+        <v>https://www.google.com/maps/place/Euro+Patisserie/@-37.8555027,145.0202229,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669dbde7cc6fb:0x3d7ede4e124dd153!8m2!3d-37.8555027!4d145.0202229!16s%2Fg%2F1tghpqv0?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K16" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v>42VC+Q3 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v>3/9/2026, 6:26:45 PM</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +1336,40 @@
         <v>https://www.google.com/maps/place/CALI+JARDIN/data=!4m7!3m6!1s0x6ad66900127501e9:0x7dbed03707e7f043!8m2!3d-37.8545691!4d145.0125345!16s%2Fg%2F11lddj2y75!19sChIJ6QF1EgBp1moRQ_DnBzfQvn0?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G17" t="str">
-        <v>3/9/2026, 6:01:35 PM</v>
+        <v>730 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H17" t="str">
+        <v>+61 3 9191 0103</v>
+      </c>
+      <c r="I17" t="str">
+        <v>http://www.calijardin.com/</v>
+      </c>
+      <c r="J17" t="str">
+        <v>https://www.google.com/maps/place/CALI+JARDIN/@-37.8545691,145.0125345,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad66900127501e9:0x7dbed03707e7f043!8m2!3d-37.8545691!4d145.0125345!16s%2Fg%2F11lddj2y75?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K17" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v>42W7+52 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v>3/9/2026, 6:26:56 PM</v>
       </c>
     </row>
     <row r="18">
@@ -805,22 +1377,55 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Armadale Park Café</v>
+        <v>Beatty and Rose Providore</v>
       </c>
       <c r="C18" t="str">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="D18" t="str">
-        <v>365</v>
+        <v>34</v>
       </c>
       <c r="E18" t="str">
-        <v>$1–20</v>
+        <v>Corner of Beatty Ave &amp;, 11 Beatty Ave</v>
       </c>
       <c r="F18" t="str">
-        <v>https://www.google.com/maps/place/Armadale+Park+Caf%C3%A9/data=!4m7!3m6!1s0x2a32936af805dcad:0x7652460bb8b809f1!8m2!3d-32.151738!4d116.015489!16s%2Fg%2F11b75jyy1q!19sChIJrdwF-GqTMioR8Qm4uAtGUnY?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Beatty+and+Rose+Providore/data=!4m7!3m6!1s0x6ad6693e5c3114cd:0x645b5b79eef55cad!8m2!3d-37.8508003!4d145.0143543!16s%2Fg%2F11fjvtp0ql!19sChIJzRQxXD5p1moRrVz17nlbW2Q?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G18" t="str">
-        <v>3/9/2026, 6:01:45 PM</v>
+        <v>Corner of Beatty Ave &amp;, 11 Beatty Ave, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v>https://www.google.com/maps/place/Beatty+and+Rose+Providore/@-37.8508003,145.0143543,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6693e5c3114cd:0x645b5b79eef55cad!8m2!3d-37.8508003!4d145.0143543!16s%2Fg%2F11fjvtp0ql?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K18" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v>42X7+MP Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v>3/9/2026, 6:27:07 PM</v>
       </c>
     </row>
     <row r="19">
@@ -828,22 +1433,55 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Beatty and Rose Providore</v>
+        <v>Green Cup Armadale</v>
       </c>
       <c r="C19" t="str">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="D19" t="str">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="E19" t="str">
-        <v>Corner of Beatty Ave &amp;, 11 Beatty Ave</v>
+        <v>$1–20</v>
       </c>
       <c r="F19" t="str">
-        <v>https://www.google.com/maps/place/Beatty+and+Rose+Providore/data=!4m7!3m6!1s0x6ad6693e5c3114cd:0x645b5b79eef55cad!8m2!3d-37.8508003!4d145.0143543!16s%2Fg%2F11fjvtp0ql!19sChIJzRQxXD5p1moRrVz17nlbW2Q?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Green+Cup+Armadale/data=!4m7!3m6!1s0x6ad669e097a5d7c3:0x13bca0446945e07f!8m2!3d-37.856667!4d145.02812!16s%2Fg%2F11ckvynh41!19sChIJw9ell-Bp1moRf-BFaUSgvBM?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G19" t="str">
-        <v>3/9/2026, 6:01:56 PM</v>
+        <v>1242 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>http://greencup.com.au/</v>
+      </c>
+      <c r="J19" t="str">
+        <v>https://www.google.com/maps/place/Green+Cup+Armadale/@-37.856667,145.02812,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669e097a5d7c3:0x13bca0446945e07f!8m2!3d-37.856667!4d145.02812!16s%2Fg%2F11ckvynh41?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K19" t="str">
+        <v>4.1</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="N19" t="str">
+        <v>42VH+86 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v>3/9/2026, 6:27:19 PM</v>
       </c>
     </row>
     <row r="20">
@@ -851,22 +1489,55 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Green Cup Armadale</v>
+        <v>8days Cafe</v>
       </c>
       <c r="C20" t="str">
         <v>4.1</v>
       </c>
       <c r="D20" t="str">
-        <v>196</v>
+        <v>330</v>
       </c>
       <c r="E20" t="str">
-        <v>$1–20</v>
+        <v>$20–40</v>
       </c>
       <c r="F20" t="str">
-        <v>https://www.google.com/maps/place/Green+Cup+Armadale/data=!4m7!3m6!1s0x6ad669e097a5d7c3:0x13bca0446945e07f!8m2!3d-37.856667!4d145.02812!16s%2Fg%2F11ckvynh41!19sChIJw9ell-Bp1moRf-BFaUSgvBM?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/8days+Cafe/data=!4m7!3m6!1s0x6ad669de2212a9ab:0x6230683dbec306fa!8m2!3d-37.8564094!4d145.0267625!16s%2Fg%2F1tqnls8j!19sChIJq6kSIt5p1moR-gbDvj1oMGI?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G20" t="str">
-        <v>3/9/2026, 6:02:09 PM</v>
+        <v>1184 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H20" t="str">
+        <v>+61 3 7013 3922</v>
+      </c>
+      <c r="I20" t="str">
+        <v>https://www.8dayscafe.com.au/</v>
+      </c>
+      <c r="J20" t="str">
+        <v>https://www.google.com/maps/place/8days+Cafe/@-37.8564094,145.0267625,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de2212a9ab:0x6230683dbec306fa!8m2!3d-37.8564094!4d145.0267625!16s%2Fg%2F1tqnls8j?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K20" t="str">
+        <v>4.1</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N20" t="str">
+        <v>42VG+CP Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Bustling, stylish cafe whipping up coffee &amp; espresso drinks, plus global breakfast &amp; lunch fare.</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v>3/9/2026, 6:27:29 PM</v>
       </c>
     </row>
     <row r="21">
@@ -874,22 +1545,55 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>8days Cafe</v>
+        <v>The Cake Club.</v>
       </c>
       <c r="C21" t="str">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="D21" t="str">
-        <v>330</v>
+        <v>127</v>
       </c>
       <c r="E21" t="str">
-        <v>$20–40</v>
+        <v>$1–20</v>
       </c>
       <c r="F21" t="str">
-        <v>https://www.google.com/maps/place/8days+Cafe/data=!4m7!3m6!1s0x6ad669de2212a9ab:0x6230683dbec306fa!8m2!3d-37.8564094!4d145.0267625!16s%2Fg%2F1tqnls8j!19sChIJq6kSIt5p1moR-gbDvj1oMGI?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/The+Cake+Club./data=!4m7!3m6!1s0x6ad66997e1cedd23:0xbbd2fa7b7159f859!8m2!3d-37.8545586!4d145.0121688!16s%2Fg%2F11kq43f6kl!19sChIJI93O4Zdp1moRWfhZcXv60rs?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G21" t="str">
-        <v>3/9/2026, 6:02:21 PM</v>
+        <v>722 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H21" t="str">
+        <v>+61 483 794 616</v>
+      </c>
+      <c r="I21" t="str">
+        <v>http://thecakeclub.co/</v>
+      </c>
+      <c r="J21" t="str">
+        <v>https://www.google.com/maps/place/The+Cake+Club./@-37.8545586,145.0121688,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad66997e1cedd23:0xbbd2fa7b7159f859!8m2!3d-37.8545586!4d145.0121688!16s%2Fg%2F11kq43f6kl?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K21" t="str">
+        <v>4.9</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="N21" t="str">
+        <v>42W6+5V Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v>3/9/2026, 6:27:41 PM</v>
       </c>
     </row>
     <row r="22">
@@ -897,22 +1601,55 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>La Dolce Vita Pizza Bar</v>
+        <v>Auterra Wine Bar</v>
       </c>
       <c r="C22" t="str">
         <v>4.7</v>
       </c>
       <c r="D22" t="str">
-        <v>76</v>
+        <v>215</v>
       </c>
       <c r="E22" t="str">
-        <v>$20–40</v>
+        <v></v>
       </c>
       <c r="F22" t="str">
-        <v>https://www.google.com/maps/place/La+Dolce+Vita+Pizza+Bar/data=!4m7!3m6!1s0x6ad669d176bcf111:0xc634fcb48386270e!8m2!3d-37.854484!4d145.011738!16s%2Fg%2F1tdzg3zt!19sChIJEfG8dtFp1moRDieGg7T8NMY?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Auterra+Wine+Bar/data=!4m7!3m6!1s0x6ad669184a3fe71b:0x21cd4a01c45abfcd!8m2!3d-37.8562794!4d145.02602!16s%2Fg%2F11nfsyk0ks!19sChIJG-c_Shhp1moRzb9axAFKzSE?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G22" t="str">
-        <v>3/9/2026, 6:02:31 PM</v>
+        <v>1160 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H22" t="str">
+        <v>+61 3 8529 2660</v>
+      </c>
+      <c r="I22" t="str">
+        <v>http://auterrawinebar.com.au/</v>
+      </c>
+      <c r="J22" t="str">
+        <v>https://www.google.com/maps/place/Auterra+Wine+Bar/@-37.8562794,145.02602,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669184a3fe71b:0x21cd4a01c45abfcd!8m2!3d-37.8562794!4d145.02602!16s%2Fg%2F11nfsyk0ks?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K22" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v>42VG+FC Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v>3/9/2026, 6:27:52 PM</v>
       </c>
     </row>
     <row r="23">
@@ -920,22 +1657,55 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Cafe Claremont</v>
+        <v>Pony</v>
       </c>
       <c r="C23" t="str">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="D23" t="str">
-        <v>305</v>
+        <v>151</v>
       </c>
       <c r="E23" t="str">
-        <v>$20–40</v>
+        <v>14 Beatty Ave</v>
       </c>
       <c r="F23" t="str">
-        <v>https://www.google.com/maps/place/Cafe+Claremont/data=!4m7!3m6!1s0x6ad669e9ac7571ef:0x47aec43ac3e3d6b8!8m2!3d-37.8657276!4d145.0296768!16s%2Fg%2F1v5k34nc!19sChIJ73F1rOlp1moRuNbjwzrErkc?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Pony/data=!4m7!3m6!1s0x6ad6699d6a445fef:0xe24e098d37e6d080!8m2!3d-37.8506722!4d145.0142614!16s%2Fg%2F11vc86kknr!19sChIJ719Eap1p1moRgNDmN40JTuI?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G23" t="str">
-        <v>3/9/2026, 6:02:41 PM</v>
+        <v>14 Beatty Ave, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H23" t="str">
+        <v>+61 3 9326 2162</v>
+      </c>
+      <c r="I23" t="str">
+        <v>http://pony.melbourne/</v>
+      </c>
+      <c r="J23" t="str">
+        <v>https://www.google.com/maps/place/Pony/@-37.8506722,145.0142614,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6699d6a445fef:0xe24e098d37e6d080!8m2!3d-37.8506722!4d145.0142614!16s%2Fg%2F11vc86kknr?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K23" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v>42X7+PP Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v>3/9/2026, 6:28:04 PM</v>
       </c>
     </row>
     <row r="24">
@@ -943,22 +1713,55 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Prickly Pear</v>
+        <v>Zia Rina's Cucina</v>
       </c>
       <c r="C24" t="str">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="D24" t="str">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E24" t="str">
-        <v>$1–20</v>
+        <v>857 High St</v>
       </c>
       <c r="F24" t="str">
-        <v>https://www.google.com/maps/place/Prickly+Pear/data=!4m7!3m6!1s0x6ad669e80f0dc7f1:0x4c9662f64975953e!8m2!3d-37.8630676!4d145.0279907!16s%2Fg%2F1pwfxh846!19sChIJ8ccND-hp1moRPpV1SfZilkw?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Zia+Rina%27s+Cucina/data=!4m7!3m6!1s0x6ad669d0a6f28359:0x6c98c51433efa1fa!8m2!3d-37.854664!4d145.016019!16s%2Fg%2F1hc2x6jgg!19sChIJWYPyptBp1moR-qHvMxTFmGw?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G24" t="str">
-        <v>3/9/2026, 6:02:53 PM</v>
+        <v>857 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>http://www.rinas3143.com/</v>
+      </c>
+      <c r="J24" t="str">
+        <v>https://www.google.com/maps/place/Zia+Rina's+Cucina/@-37.854664,145.016019,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d0a6f28359:0x6c98c51433efa1fa!8m2!3d-37.854664!4d145.016019!16s%2Fg%2F1hc2x6jgg?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K24" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v>42W8+4C Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v>3/9/2026, 6:28:16 PM</v>
       </c>
     </row>
     <row r="25">
@@ -966,22 +1769,55 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Zia Rina's Cucina</v>
+        <v>Jack's House Cafe</v>
       </c>
       <c r="C25" t="str">
         <v>4.6</v>
       </c>
       <c r="D25" t="str">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="E25" t="str">
-        <v>857 High St</v>
+        <v>$20–40</v>
       </c>
       <c r="F25" t="str">
-        <v>https://www.google.com/maps/place/Zia+Rina%27s+Cucina/data=!4m7!3m6!1s0x6ad669d0a6f28359:0x6c98c51433efa1fa!8m2!3d-37.854664!4d145.016019!16s%2Fg%2F1hc2x6jgg!19sChIJWYPyptBp1moR-qHvMxTFmGw?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Jack%27s+House+Cafe/data=!4m7!3m6!1s0x6ad669fd4213e46f:0xac9c9b2bf55099a7!8m2!3d-37.8580501!4d145.0396302!16s%2Fg%2F11g0g2b711!19sChIJb-QTQv1p1moRp5lQ9SubnKw?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G25" t="str">
-        <v>3/9/2026, 6:03:04 PM</v>
+        <v>1398 High St, Malvern VIC 3144, Australia</v>
+      </c>
+      <c r="H25" t="str">
+        <v>+61 405 169 055</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>https://www.google.com/maps/place/Jack's+House+Cafe/@-37.8580501,145.0396302,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669fd4213e46f:0xac9c9b2bf55099a7!8m2!3d-37.8580501!4d145.0396302!16s%2Fg%2F11g0g2b711?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K25" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N25" t="str">
+        <v>42RQ+QV Malvern, Victoria, Australia</v>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v>3/9/2026, 6:28:25 PM</v>
       </c>
     </row>
     <row r="26">
@@ -989,22 +1825,55 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>One Origin Specialty Coffee</v>
+        <v>Bouzy Bar Armadale</v>
       </c>
       <c r="C26" t="str">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="D26" t="str">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="E26" t="str">
-        <v>$1–20</v>
+        <v>976 High St</v>
       </c>
       <c r="F26" t="str">
-        <v>https://www.google.com/maps/place/One+Origin+Specialty+Coffee/data=!4m7!3m6!1s0x6ad669e805e57263:0x7cc3e7704a159166!8m2!3d-37.862954!4d145.027984!16s%2Fg%2F11b64ny2gh!19sChIJY3LlBehp1moRZpEVSnDnw3w?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Bouzy+Bar+Armadale/data=!4m7!3m6!1s0x6ad6695501d31029:0x8a5205e762ad2ea3!8m2!3d-37.8556142!4d145.0203607!16s%2Fg%2F11y623dph3!19sChIJKRDTAVVp1moRoy6tYucFUoo?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G26" t="str">
-        <v>3/9/2026, 6:03:14 PM</v>
+        <v>976 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>https://www.bouzy.au/</v>
+      </c>
+      <c r="J26" t="str">
+        <v>https://www.google.com/maps/place/Bouzy+Bar+Armadale/@-37.8556142,145.0203607,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6695501d31029:0x8a5205e762ad2ea3!8m2!3d-37.8556142!4d145.0203607!16s%2Fg%2F11y623dph3?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K26" t="str">
+        <v>4.6</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v>42VC+Q4 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v>3/9/2026, 6:28:35 PM</v>
       </c>
     </row>
     <row r="27">
@@ -1012,22 +1881,55 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>Auterra Wine Bar</v>
+        <v>Amaru</v>
       </c>
       <c r="C27" t="str">
         <v>4.7</v>
       </c>
       <c r="D27" t="str">
-        <v>215</v>
+        <v>522</v>
       </c>
       <c r="E27" t="str">
-        <v></v>
+        <v>$200+</v>
       </c>
       <c r="F27" t="str">
-        <v>https://www.google.com/maps/place/Auterra+Wine+Bar/data=!4m7!3m6!1s0x6ad669184a3fe71b:0x21cd4a01c45abfcd!8m2!3d-37.8562794!4d145.02602!16s%2Fg%2F11nfsyk0ks!19sChIJG-c_Shhp1moRzb9axAFKzSE?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Amaru/data=!4m7!3m6!1s0x6ad669de5e639241:0xe32e752ff825edf1!8m2!3d-37.8558133!4d145.0249461!16s%2Fg%2F11cjp_p_hl!19sChIJQZJjXt5p1moR8e0l-C91LuM?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G27" t="str">
-        <v>3/9/2026, 6:03:27 PM</v>
+        <v>1121 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H27" t="str">
+        <v>+61 420 391 732</v>
+      </c>
+      <c r="I27" t="str">
+        <v>http://amarumelbourne.com.au/</v>
+      </c>
+      <c r="J27" t="str">
+        <v>https://www.google.com/maps/place/Amaru/@-37.8558133,145.0249461,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de5e639241:0xe32e752ff825edf1!8m2!3d-37.8558133!4d145.0249461!16s%2Fg%2F11cjp_p_hl?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K27" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>$200+</v>
+      </c>
+      <c r="N27" t="str">
+        <v>42VF+MX Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v>3/9/2026, 6:28:45 PM</v>
       </c>
     </row>
     <row r="28">
@@ -1035,22 +1937,55 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>The Green Goose</v>
+        <v>Cafe Latte</v>
       </c>
       <c r="C28" t="str">
         <v>4.5</v>
       </c>
       <c r="D28" t="str">
-        <v>189</v>
+        <v>284</v>
       </c>
       <c r="E28" t="str">
-        <v>$1–20</v>
+        <v>$20–40</v>
       </c>
       <c r="F28" t="str">
-        <v>https://www.google.com/maps/place/The+Green+Goose/data=!4m7!3m6!1s0x6ad669e831bbf865:0x47c0e6df2fbb4aba!8m2!3d-37.8647919!4d145.0283764!16s%2Fg%2F1tx_6hns!19sChIJZfi7Mehp1moRukq7L9_mwEc?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Cafe+Latte/data=!4m7!3m6!1s0x6ad6682b17e1b84b:0x8494ab429665d4d0!8m2!3d-37.8480169!4d145.0038932!16s%2Fg%2F1tls2zw_!19sChIJS7jhFyto1moR0NRllkKrlIQ?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G28" t="str">
-        <v>3/9/2026, 6:03:38 PM</v>
+        <v>521 Malvern Rd, Toorak VIC 3142, Australia</v>
+      </c>
+      <c r="H28" t="str">
+        <v>+61 3 7036 0084</v>
+      </c>
+      <c r="I28" t="str">
+        <v>https://www.cafelattehawksburn.com/</v>
+      </c>
+      <c r="J28" t="str">
+        <v>https://www.google.com/maps/place/Cafe+Latte/@-37.8480169,145.0038932,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6682b17e1b84b:0x8494ab429665d4d0!8m2!3d-37.8480169!4d145.0038932!16s%2Fg%2F1tls2zw_?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K28" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N28" t="str">
+        <v>5223+QH Toorak, Victoria, Australia</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Modern cafe offering breakfast, lunch &amp; brunch, plus  a variety of coffee drinks.</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v>3/9/2026, 6:28:57 PM</v>
       </c>
     </row>
     <row r="29">
@@ -1058,22 +1993,55 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Cafe Latte</v>
+        <v>Victor Churchill</v>
       </c>
       <c r="C29" t="str">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="D29" t="str">
-        <v>284</v>
+        <v>695</v>
       </c>
       <c r="E29" t="str">
-        <v>$20–40</v>
+        <v></v>
       </c>
       <c r="F29" t="str">
-        <v>https://www.google.com/maps/place/Cafe+Latte/data=!4m7!3m6!1s0x6ad6682b17e1b84b:0x8494ab429665d4d0!8m2!3d-37.8480169!4d145.0038932!16s%2Fg%2F1tls2zw_!19sChIJS7jhFyto1moR0NRllkKrlIQ?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Victor+Churchill/data=!4m7!3m6!1s0x6ad669f5c4a83fed:0x54037a72852158f7!8m2!3d-37.8552206!4d145.020079!16s%2Fg%2F11pc9nmtsn!19sChIJ7T-oxPVp1moR91ghhXJ6A1Q?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G29" t="str">
-        <v>3/9/2026, 6:03:49 PM</v>
+        <v>953 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H29" t="str">
+        <v>+61 3 9978 1968</v>
+      </c>
+      <c r="I29" t="str">
+        <v>https://victorchurchill.com/pages/melbourne/?utm_source=google+my+business&amp;utm_medium=organic</v>
+      </c>
+      <c r="J29" t="str">
+        <v>https://www.google.com/maps/place/Victor+Churchill/@-37.8552206,145.020079,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669f5c4a83fed:0x54037a72852158f7!8m2!3d-37.8552206!4d145.020079!16s%2Fg%2F11pc9nmtsn?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K29" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v>42VC+W2 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v>3/9/2026, 6:29:08 PM</v>
       </c>
     </row>
     <row r="30">
@@ -1081,22 +2049,55 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Eden Espresso</v>
+        <v>Thirty Mill</v>
       </c>
       <c r="C30" t="str">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="D30" t="str">
-        <v>501</v>
+        <v>362</v>
       </c>
       <c r="E30" t="str">
         <v>$20–40</v>
       </c>
       <c r="F30" t="str">
-        <v>https://www.google.com/maps/place/Eden+Espresso/data=!4m7!3m6!1s0x6ad669e7ec765027:0x897d2a0ba7fff158!8m2!3d-37.861934!4d145.0281!16s%2Fg%2F1wfvmsyb!19sChIJJ1B27Odp1moRWPH_pwsqfYk?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Thirty+Mill/data=!4m7!3m6!1s0x6ad6420520e26267:0x557c61df6741dc78!8m2!3d-37.8493455!4d145.0408918!16s%2Fg%2F1tgmwf0n!19sChIJZ2LiIAVC1moReNxBZ99hfFU?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G30" t="str">
-        <v>3/9/2026, 6:04:03 PM</v>
+        <v>66 Milton Parade, Malvern VIC 3144, Australia</v>
+      </c>
+      <c r="H30" t="str">
+        <v>+61 3 9804 3653</v>
+      </c>
+      <c r="I30" t="str">
+        <v>https://www.thirtymill.com/</v>
+      </c>
+      <c r="J30" t="str">
+        <v>https://www.google.com/maps/place/Thirty+Mill/@-37.8493455,145.0408918,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6420520e26267:0x557c61df6741dc78!8m2!3d-37.8493455!4d145.0408918!16s%2Fg%2F1tgmwf0n?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K30" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="N30" t="str">
+        <v>522R+79 Malvern, Victoria, Australia</v>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v>3/9/2026, 6:29:20 PM</v>
       </c>
     </row>
     <row r="31">
@@ -1104,34 +2105,67 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Bottega Bistró</v>
+        <v>Phillippa's Bakery</v>
       </c>
       <c r="C31" t="str">
-        <v>4.8</v>
+        <v>4.0</v>
       </c>
       <c r="D31" t="str">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="E31" t="str">
-        <v>$60–80</v>
+        <v>$1–20</v>
       </c>
       <c r="F31" t="str">
-        <v>https://www.google.com/maps/place/Bottega+Bistr%C3%B3/data=!4m7!3m6!1s0x6ad66944465f64b7:0x22f82aacbbd23933!8m2!3d-37.8503547!4d145.0140412!16s%2Fg%2F11md97hlkw!19sChIJt2RfRkRp1moRMznSu6wq-CI?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v>https://www.google.com/maps/place/Phillippa%27s+Bakery/data=!4m7!3m6!1s0x6ad669d9550dd479:0xf2ae5dae0da13b22!8m2!3d-37.8557517!4d145.021603!16s%2Fg%2F1v2jd1dn!19sChIJedQNVdlp1moRIjuhDa5drvI?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="G31" t="str">
-        <v>3/9/2026, 6:04:15 PM</v>
+        <v>1030 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="H31" t="str">
+        <v>+61 3 9576 2020</v>
+      </c>
+      <c r="I31" t="str">
+        <v>http://www.phillippas.com.au/</v>
+      </c>
+      <c r="J31" t="str">
+        <v>https://www.google.com/maps/place/Phillippa's+Bakery/@-37.8557517,145.021603,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d9550dd479:0xf2ae5dae0da13b22!8m2!3d-37.8557517!4d145.021603!16s%2Fg%2F1v2jd1dn?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="K31" t="str">
+        <v>4.0</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="N31" t="str">
+        <v>42VC+MJ Armadale, Victoria, Australia</v>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v>3/9/2026, 6:29:31 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1183,63 +2217,111 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Businesses with Phone</v>
+        <v>Businesses with Address</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Businesses with Website</v>
+        <v>Businesses with Phone</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Businesses with Email</v>
+        <v>Businesses with Website</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Businesses with Hours</v>
+        <v>Businesses with Email</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v/>
+        <v>Businesses with Hours</v>
+      </c>
+      <c r="B11">
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Extraction Date</v>
+        <v/>
       </c>
       <c r="B12" t="str">
-        <v>3/9/2026, 6:04:15 PM</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>Extraction Date</v>
+      </c>
+      <c r="B13" t="str">
+        <v>3/9/2026, 6:29:31 PM</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
         <v>Data Sheet</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B14" t="str">
         <v>Businesses</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Rating Statistics</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Average Rating</v>
+      </c>
+      <c r="B17" t="str">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Highest Rating</v>
+      </c>
+      <c r="B18" t="str">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Lowest Rating</v>
+      </c>
+      <c r="B19" t="str">
+        <v>4.0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/malvern-cafes.xlsx
+++ b/malvern-cafes.xlsx
@@ -398,26 +398,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:Q31"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" customWidth="1"/>
-    <col min="5" max="5" width="39.83203125" customWidth="1"/>
-    <col min="6" max="6" width="100.83203125" customWidth="1"/>
-    <col min="7" max="7" width="69.83203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="100.83203125" customWidth="1"/>
-    <col min="10" max="10" width="100.83203125" customWidth="1"/>
-    <col min="11" max="11" width="17.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="13" width="13.83203125" customWidth="1"/>
-    <col min="14" max="14" width="39.83203125" customWidth="1"/>
-    <col min="15" max="15" width="98.83203125" customWidth="1"/>
-    <col min="16" max="16" width="29.83203125" customWidth="1"/>
-    <col min="17" max="17" width="15.83203125" customWidth="1"/>
-    <col min="18" max="18" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="69.83203125" customWidth="1"/>
+    <col min="5" max="5" width="100.83203125" customWidth="1"/>
+    <col min="6" max="6" width="29.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="39.83203125" customWidth="1"/>
+    <col min="12" max="12" width="39.83203125" customWidth="1"/>
+    <col min="13" max="13" width="100.83203125" customWidth="1"/>
+    <col min="14" max="14" width="100.83203125" customWidth="1"/>
+    <col min="15" max="15" width="100.83203125" customWidth="1"/>
+    <col min="16" max="16" width="15.83203125" customWidth="1"/>
+    <col min="17" max="17" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -428,51 +427,48 @@
         <v>Business Name</v>
       </c>
       <c r="C1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Address</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Website</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="G1" t="str">
         <v>Rating</v>
       </c>
-      <c r="D1" t="str">
-        <v>Reviews</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Price Range (Listing)</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
+        <v>Total Reviews</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Reviews Count</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Price Range</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Price (Listing)</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Plus Code</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Google Maps URL</v>
+      </c>
+      <c r="N1" t="str">
         <v>Listing Link</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Full Address</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Website</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Google Maps URL</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Detailed Rating</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Total Reviews</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Price Range</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Plus Code</v>
       </c>
       <c r="O1" t="str">
         <v>Description</v>
       </c>
       <c r="P1" t="str">
-        <v>Email</v>
+        <v>Check-in Time</v>
       </c>
       <c r="Q1" t="str">
-        <v>Check-in Time</v>
-      </c>
-      <c r="R1" t="str">
         <v>Extracted At</v>
       </c>
     </row>
@@ -484,41 +480,41 @@
         <v>High Society</v>
       </c>
       <c r="C2" t="str">
+        <v>+61 3 8578 4602</v>
+      </c>
+      <c r="D2" t="str">
+        <v>1102 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E2" t="str">
+        <v>https://www.highsocietyarmadale.com/</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <v>4.3</v>
       </c>
-      <c r="D2" t="str">
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>620</v>
       </c>
-      <c r="E2" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="F2" t="str">
+      <c r="J2" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="K2" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="L2" t="str">
+        <v>42VF+HH Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M2" t="str">
+        <v>https://www.google.com/maps/place/High+Society/@-37.8560263,145.0239643,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de84ea1b2f:0xdab68fcd9a2b0276!8m2!3d-37.8560263!4d145.0239643!16s%2Fg%2F11cjj62kzc?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N2" t="str">
         <v>https://www.google.com/maps/place/High+Society/data=!4m7!3m6!1s0x6ad669de84ea1b2f:0xdab68fcd9a2b0276!8m2!3d-37.8560263!4d145.0239643!16s%2Fg%2F11cjj62kzc!19sChIJLxvqhN5p1moRdgIrms2Ptto?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G2" t="str">
-        <v>1102 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H2" t="str">
-        <v>+61 3 8578 4602</v>
-      </c>
-      <c r="I2" t="str">
-        <v>https://www.highsocietyarmadale.com/</v>
-      </c>
-      <c r="J2" t="str">
-        <v>https://www.google.com/maps/place/High+Society/@-37.8560263,145.0239643,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de84ea1b2f:0xdab68fcd9a2b0276!8m2!3d-37.8560263!4d145.0239643!16s%2Fg%2F11cjj62kzc?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K2" t="str">
-        <v>4.3</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="N2" t="str">
-        <v>42VF+HH Armadale, Victoria, Australia</v>
-      </c>
       <c r="O2" t="str">
         <v/>
       </c>
@@ -526,10 +522,7 @@
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v>3/9/2026, 6:24:11 PM</v>
+        <v>3/9/2026, 6:42:32 PM</v>
       </c>
     </row>
     <row r="3">
@@ -537,43 +530,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Small Wins (Previously Nine Yards)</v>
+        <v>Mammoth Cafe Armadale</v>
       </c>
       <c r="C3" t="str">
-        <v>4.6</v>
+        <v>+61 3 9824 5239</v>
       </c>
       <c r="D3" t="str">
-        <v>326</v>
+        <v>736 Malvern Rd, Armadale VIC 3143, Australia</v>
       </c>
       <c r="E3" t="str">
-        <v>$20–40</v>
+        <v>https://mammotharmadale.com.au/</v>
       </c>
       <c r="F3" t="str">
-        <v>https://www.google.com/maps/place/Small+Wins+%28Previously+Nine+Yards%29/data=!4m7!3m6!1s0x6ad669c45f8dcb1f:0xd734227b45981edc!8m2!3d-37.8562109!4d145.0278178!16s%2Fg%2F11kzvgcx5_!19sChIJH8uNX8Rp1moR3B6YRXsiNNc?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>1203 High St, Armadale VIC 3143, Australia</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="str">
-        <v>+61 3 9822 2014</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>https://linktr.ee/smallwins.armadale?utm_source=linktree_profile_share&amp;ltsid=637f127c-3936-408c-bdcb-1fa168d731d3</v>
+        <v>648</v>
       </c>
       <c r="J3" t="str">
-        <v>https://www.google.com/maps/place/Small+Wins+(Previously+Nine+Yards)/@-37.8562109,145.0278178,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669c45f8dcb1f:0xd734227b45981edc!8m2!3d-37.8562109!4d145.0278178!16s%2Fg%2F11kzvgcx5_?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$20–40</v>
       </c>
       <c r="K3" t="str">
-        <v>4.6</v>
+        <v>$20–40</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>5227+57 Armadale, Victoria, Australia</v>
       </c>
       <c r="M3" t="str">
-        <v>$20–40</v>
+        <v>https://www.google.com/maps/place/Mammoth+Cafe+Armadale/@-37.849539,145.013157,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d64986365d:0xd89d1592f5b895c1!8m2!3d-37.849539!4d145.013157!16s%2Fg%2F11bw51sknh?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N3" t="str">
-        <v>42VH+G4 Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Mammoth+Cafe+Armadale/data=!4m7!3m6!1s0x6ad669d64986365d:0xd89d1592f5b895c1!8m2!3d-37.849539!4d145.013157!16s%2Fg%2F11bw51sknh!19sChIJXTaGSdZp1moRwZW49ZIVndg?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -582,10 +575,7 @@
         <v/>
       </c>
       <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v>3/9/2026, 6:24:20 PM</v>
+        <v>3/9/2026, 6:42:42 PM</v>
       </c>
     </row>
     <row r="4">
@@ -593,43 +583,43 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Mammoth Cafe Armadale</v>
+        <v>Small Wins (Previously Nine Yards)</v>
       </c>
       <c r="C4" t="str">
-        <v>4.3</v>
+        <v>+61 3 9822 2014</v>
       </c>
       <c r="D4" t="str">
-        <v>648</v>
+        <v>1203 High St, Armadale VIC 3143, Australia</v>
       </c>
       <c r="E4" t="str">
-        <v>$20–40</v>
+        <v>https://linktr.ee/smallwins.armadale?utm_source=linktree_profile_share&amp;ltsid=637f127c-3936-408c-bdcb-1fa168d731d3</v>
       </c>
       <c r="F4" t="str">
-        <v>https://www.google.com/maps/place/Mammoth+Cafe+Armadale/data=!4m7!3m6!1s0x6ad669d64986365d:0xd89d1592f5b895c1!8m2!3d-37.849539!4d145.013157!16s%2Fg%2F11bw51sknh!19sChIJXTaGSdZp1moRwZW49ZIVndg?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>736 Malvern Rd, Armadale VIC 3143, Australia</v>
+        <v>4.6</v>
       </c>
       <c r="H4" t="str">
-        <v>+61 3 9824 5239</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>https://mammotharmadale.com.au/</v>
+        <v>326</v>
       </c>
       <c r="J4" t="str">
-        <v>https://www.google.com/maps/place/Mammoth+Cafe+Armadale/@-37.849539,145.013157,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d64986365d:0xd89d1592f5b895c1!8m2!3d-37.849539!4d145.013157!16s%2Fg%2F11bw51sknh?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$20–40</v>
       </c>
       <c r="K4" t="str">
-        <v>4.3</v>
+        <v>$20–40</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>42VH+G4 Armadale, Victoria, Australia</v>
       </c>
       <c r="M4" t="str">
-        <v>$20–40</v>
+        <v>https://www.google.com/maps/place/Small+Wins+(Previously+Nine+Yards)/@-37.8562109,145.0278178,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669c45f8dcb1f:0xd734227b45981edc!8m2!3d-37.8562109!4d145.0278178!16s%2Fg%2F11kzvgcx5_?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N4" t="str">
-        <v>5227+57 Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Small+Wins+%28Previously+Nine+Yards%29/data=!4m7!3m6!1s0x6ad669c45f8dcb1f:0xd734227b45981edc!8m2!3d-37.8562109!4d145.0278178!16s%2Fg%2F11kzvgcx5_!19sChIJH8uNX8Rp1moR3B6YRXsiNNc?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -638,10 +628,7 @@
         <v/>
       </c>
       <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v>3/9/2026, 6:24:31 PM</v>
+        <v>3/9/2026, 6:42:53 PM</v>
       </c>
     </row>
     <row r="5">
@@ -652,41 +639,41 @@
         <v>Coffee Ministry Armadale</v>
       </c>
       <c r="C5" t="str">
+        <v>+61 478 895 749</v>
+      </c>
+      <c r="D5" t="str">
+        <v>59A Armadale St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
         <v>4.7</v>
       </c>
-      <c r="D5" t="str">
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>26</v>
       </c>
-      <c r="E5" t="str">
+      <c r="J5" t="str">
         <v>$1–20</v>
       </c>
-      <c r="F5" t="str">
+      <c r="K5" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="L5" t="str">
+        <v>42V9+8C Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M5" t="str">
+        <v>https://www.google.com/maps/place/Coffee+Ministry+Armadale/@-37.8567013,145.0186063,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669432bb51f17:0xea4d193a38f79d53!8m2!3d-37.8567013!4d145.0186063!16s%2Fg%2F11vz35bn0y?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N5" t="str">
         <v>https://www.google.com/maps/place/Coffee+Ministry+Armadale/data=!4m7!3m6!1s0x6ad669432bb51f17:0xea4d193a38f79d53!8m2!3d-37.8567013!4d145.0186063!16s%2Fg%2F11vz35bn0y!19sChIJFx-1K0Np1moRU533ODoZTeo?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G5" t="str">
-        <v>59A Armadale St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H5" t="str">
-        <v>+61 478 895 749</v>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v>https://www.google.com/maps/place/Coffee+Ministry+Armadale/@-37.8567013,145.0186063,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669432bb51f17:0xea4d193a38f79d53!8m2!3d-37.8567013!4d145.0186063!16s%2Fg%2F11vz35bn0y?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K5" t="str">
-        <v>4.7</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>$1–20</v>
-      </c>
-      <c r="N5" t="str">
-        <v>42V9+8C Armadale, Victoria, Australia</v>
-      </c>
       <c r="O5" t="str">
         <v/>
       </c>
@@ -694,10 +681,7 @@
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v>3/9/2026, 6:24:41 PM</v>
+        <v>3/9/2026, 6:43:06 PM</v>
       </c>
     </row>
     <row r="6">
@@ -708,41 +692,41 @@
         <v>Nigel</v>
       </c>
       <c r="C6" t="str">
+        <v>+61 3 8678 4080</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1268 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E6" t="str">
+        <v>https://www.nigelcoffee.com.au/</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
         <v>4.4</v>
       </c>
-      <c r="D6" t="str">
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>92</v>
       </c>
-      <c r="E6" t="str">
+      <c r="J6" t="str">
         <v>$1–20</v>
       </c>
-      <c r="F6" t="str">
+      <c r="K6" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="L6" t="str">
+        <v>42VH+8G Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M6" t="str">
+        <v>https://www.google.com/maps/place/Nigel/@-37.856745,145.028871,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669626445af73:0xbeab4aab55e5322e!8m2!3d-37.856745!4d145.028871!16s%2Fg%2F11r9vw8v_v?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N6" t="str">
         <v>https://www.google.com/maps/place/Nigel/data=!4m7!3m6!1s0x6ad669626445af73:0xbeab4aab55e5322e!8m2!3d-37.856745!4d145.028871!16s%2Fg%2F11r9vw8v_v!19sChIJc69FZGJp1moRLjLlVatKq74?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G6" t="str">
-        <v>1268 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H6" t="str">
-        <v>+61 3 8678 4080</v>
-      </c>
-      <c r="I6" t="str">
-        <v>https://www.nigelcoffee.com.au/</v>
-      </c>
-      <c r="J6" t="str">
-        <v>https://www.google.com/maps/place/Nigel/@-37.856745,145.028871,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669626445af73:0xbeab4aab55e5322e!8m2!3d-37.856745!4d145.028871!16s%2Fg%2F11r9vw8v_v?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K6" t="str">
-        <v>4.4</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v>$1–20</v>
-      </c>
-      <c r="N6" t="str">
-        <v>42VH+8G Armadale, Victoria, Australia</v>
-      </c>
       <c r="O6" t="str">
         <v/>
       </c>
@@ -750,10 +734,7 @@
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v/>
-      </c>
-      <c r="R6" t="str">
-        <v>3/9/2026, 6:24:53 PM</v>
+        <v>3/9/2026, 6:43:17 PM</v>
       </c>
     </row>
     <row r="7">
@@ -764,41 +745,41 @@
         <v>Moby</v>
       </c>
       <c r="C7" t="str">
+        <v>+61 3 9509 2710</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1150 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E7" t="str">
+        <v>http://www.moby3143.com.au/</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
         <v>4.1</v>
       </c>
-      <c r="D7" t="str">
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v>573</v>
       </c>
-      <c r="E7" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="F7" t="str">
+      <c r="J7" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="K7" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="L7" t="str">
+        <v>42VG+G6 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M7" t="str">
+        <v>https://www.google.com/maps/place/Moby/@-37.8562195,145.0255233,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de6f13bb59:0x4e6febc121ab688b!8m2!3d-37.8562195!4d145.0255233!16s%2Fg%2F11c2jv76j3?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N7" t="str">
         <v>https://www.google.com/maps/place/Moby/data=!4m7!3m6!1s0x6ad669de6f13bb59:0x4e6febc121ab688b!8m2!3d-37.8562195!4d145.0255233!16s%2Fg%2F11c2jv76j3!19sChIJWbsTb95p1moRi2irIcHrb04?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G7" t="str">
-        <v>1150 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H7" t="str">
-        <v>+61 3 9509 2710</v>
-      </c>
-      <c r="I7" t="str">
-        <v>http://www.moby3143.com.au/</v>
-      </c>
-      <c r="J7" t="str">
-        <v>https://www.google.com/maps/place/Moby/@-37.8562195,145.0255233,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de6f13bb59:0x4e6febc121ab688b!8m2!3d-37.8562195!4d145.0255233!16s%2Fg%2F11c2jv76j3?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K7" t="str">
-        <v>4.1</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="N7" t="str">
-        <v>42VG+G6 Armadale, Victoria, Australia</v>
-      </c>
       <c r="O7" t="str">
         <v/>
       </c>
@@ -806,10 +787,7 @@
         <v/>
       </c>
       <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v>3/9/2026, 6:25:03 PM</v>
+        <v>3/9/2026, 6:43:29 PM</v>
       </c>
     </row>
     <row r="8">
@@ -820,41 +798,41 @@
         <v>Bruno&amp;Co</v>
       </c>
       <c r="C8" t="str">
+        <v>+61 3 9822 8515</v>
+      </c>
+      <c r="D8" t="str">
+        <v>1007 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E8" t="str">
+        <v>https://brunoandco.com/</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
         <v>4.5</v>
       </c>
-      <c r="D8" t="str">
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>239</v>
       </c>
-      <c r="E8" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="F8" t="str">
+      <c r="J8" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="K8" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="L8" t="str">
+        <v>42VC+RC Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M8" t="str">
+        <v>https://www.google.com/maps/place/Bruno%26Co/@-37.8553894,145.0210376,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d959c2b787:0x4295029db5ebfd16!8m2!3d-37.8553894!4d145.0210376!16s%2Fg%2F11g8nzfvc0?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N8" t="str">
         <v>https://www.google.com/maps/place/Bruno%26Co/data=!4m7!3m6!1s0x6ad669d959c2b787:0x4295029db5ebfd16!8m2!3d-37.8553894!4d145.0210376!16s%2Fg%2F11g8nzfvc0!19sChIJh7fCWdlp1moRFv3rtZ0ClUI?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G8" t="str">
-        <v>1007 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H8" t="str">
-        <v>+61 3 9822 8515</v>
-      </c>
-      <c r="I8" t="str">
-        <v>https://brunoandco.com/</v>
-      </c>
-      <c r="J8" t="str">
-        <v>https://www.google.com/maps/place/Bruno%26Co/@-37.8553894,145.0210376,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d959c2b787:0x4295029db5ebfd16!8m2!3d-37.8553894!4d145.0210376!16s%2Fg%2F11g8nzfvc0?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K8" t="str">
-        <v>4.5</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="N8" t="str">
-        <v>42VC+RC Armadale, Victoria, Australia</v>
-      </c>
       <c r="O8" t="str">
         <v/>
       </c>
@@ -862,10 +840,7 @@
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <v>3/9/2026, 6:25:16 PM</v>
+        <v>3/9/2026, 6:43:41 PM</v>
       </c>
     </row>
     <row r="9">
@@ -873,55 +848,52 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Coin Laundry Cafe</v>
+        <v>Cubbyhouse Canteen</v>
       </c>
       <c r="C9" t="str">
+        <v>+61 421 173 886</v>
+      </c>
+      <c r="D9" t="str">
+        <v>43A Union St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E9" t="str">
+        <v>https://www.cubbyhousecanteen.com.au/</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
         <v>4.4</v>
       </c>
-      <c r="D9" t="str">
-        <v>473</v>
-      </c>
-      <c r="E9" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="F9" t="str">
-        <v>https://www.google.com/maps/place/Coin+Laundry+Cafe/data=!4m7!3m6!1s0x6ad669da5253ec73:0xf5f9f549eed96d7!8m2!3d-37.856665!4d145.0186204!16s%2Fg%2F1tgw5509!19sChIJc-xTUtpp1moR15btnlSfXw8?authuser=0&amp;hl=en&amp;rclk=1</v>
-      </c>
-      <c r="G9" t="str">
-        <v>61 Armadale St, Armadale VIC 3143, Australia</v>
-      </c>
       <c r="H9" t="str">
-        <v>+61 3 9500 1888</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>139</v>
       </c>
       <c r="J9" t="str">
-        <v>https://www.google.com/maps/place/Coin+Laundry+Cafe/@-37.856665,145.0186204,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669da5253ec73:0xf5f9f549eed96d7!8m2!3d-37.856665!4d145.0186204!16s%2Fg%2F1tgw5509?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$1–20</v>
       </c>
       <c r="K9" t="str">
-        <v>4.4</v>
+        <v>$1–20</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>42RF+M9 Armadale, Victoria, Australia</v>
       </c>
       <c r="M9" t="str">
-        <v>$20–40</v>
+        <v>https://www.google.com/maps/place/Cubbyhouse+Canteen/@-37.8583368,145.0234773,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669dcf5747179:0xdf909f92969a2708!8m2!3d-37.8583368!4d145.0234773!16s%2Fg%2F12qgl7jmj?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N9" t="str">
-        <v>42V9+8C Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Cubbyhouse+Canteen/data=!4m7!3m6!1s0x6ad669dcf5747179:0xdf909f92969a2708!8m2!3d-37.8583368!4d145.0234773!16s%2Fg%2F12qgl7jmj!19sChIJeXF09dxp1moRCCealpKfkN8?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O9" t="str">
-        <v>Bustling coffeehouse in a refurbished laundromat, serving inventive breakfast and lunch dishes.</v>
+        <v/>
       </c>
       <c r="P9" t="str">
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <v>3/9/2026, 6:25:27 PM</v>
+        <v>3/9/2026, 6:43:52 PM</v>
       </c>
     </row>
     <row r="10">
@@ -929,55 +901,52 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Pique Nique</v>
+        <v>Coin Laundry Cafe</v>
       </c>
       <c r="C10" t="str">
+        <v>+61 3 9500 1888</v>
+      </c>
+      <c r="D10" t="str">
+        <v>61 Armadale St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
         <v>4.4</v>
       </c>
-      <c r="D10" t="str">
-        <v>186</v>
-      </c>
-      <c r="E10" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="F10" t="str">
-        <v>https://www.google.com/maps/place/Pique+Nique/data=!4m7!3m6!1s0x6ad669dc8a3b11fd:0x5c78c291e96d657!8m2!3d-37.8586088!4d145.0228889!16s%2Fg%2F1pzrk8chz!19sChIJ_RE7itxp1moRV9aWHimMxwU?authuser=0&amp;hl=en&amp;rclk=1</v>
-      </c>
-      <c r="G10" t="str">
-        <v>43 Union St, Armadale VIC 3143, Australia</v>
-      </c>
       <c r="H10" t="str">
-        <v>+61 412 943 999</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>473</v>
       </c>
       <c r="J10" t="str">
-        <v>https://www.google.com/maps/place/Pique+Nique/@-37.8586088,145.0228889,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669dc8a3b11fd:0x5c78c291e96d657!8m2!3d-37.8586088!4d145.0228889!16s%2Fg%2F1pzrk8chz?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$20–40</v>
       </c>
       <c r="K10" t="str">
-        <v>4.4</v>
+        <v>$20–40</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>42V9+8C Armadale, Victoria, Australia</v>
       </c>
       <c r="M10" t="str">
-        <v>$20–40</v>
+        <v>https://www.google.com/maps/place/Coin+Laundry+Cafe/@-37.856665,145.0186204,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669da5253ec73:0xf5f9f549eed96d7!8m2!3d-37.856665!4d145.0186204!16s%2Fg%2F1tgw5509?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N10" t="str">
-        <v>42RF+H5 Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Coin+Laundry+Cafe/data=!4m7!3m6!1s0x6ad669da5253ec73:0xf5f9f549eed96d7!8m2!3d-37.856665!4d145.0186204!16s%2Fg%2F1tgw5509!19sChIJc-xTUtpp1moR15btnlSfXw8?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O10" t="str">
-        <v/>
+        <v>Bustling coffeehouse in a refurbished laundromat, serving inventive breakfast and lunch dishes.</v>
       </c>
       <c r="P10" t="str">
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v/>
-      </c>
-      <c r="R10" t="str">
-        <v>3/9/2026, 6:25:36 PM</v>
+        <v>3/9/2026, 6:44:03 PM</v>
       </c>
     </row>
     <row r="11">
@@ -985,43 +954,43 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Cubbyhouse Canteen</v>
+        <v>Pique Nique</v>
       </c>
       <c r="C11" t="str">
+        <v>+61 412 943 999</v>
+      </c>
+      <c r="D11" t="str">
+        <v>43 Union St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
         <v>4.4</v>
       </c>
-      <c r="D11" t="str">
-        <v>139</v>
-      </c>
-      <c r="E11" t="str">
-        <v>$1–20</v>
-      </c>
-      <c r="F11" t="str">
-        <v>https://www.google.com/maps/place/Cubbyhouse+Canteen/data=!4m7!3m6!1s0x6ad669dcf5747179:0xdf909f92969a2708!8m2!3d-37.8583368!4d145.0234773!16s%2Fg%2F12qgl7jmj!19sChIJeXF09dxp1moRCCealpKfkN8?authuser=0&amp;hl=en&amp;rclk=1</v>
-      </c>
-      <c r="G11" t="str">
-        <v>43A Union St, Armadale VIC 3143, Australia</v>
-      </c>
       <c r="H11" t="str">
-        <v>+61 421 173 886</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>https://www.cubbyhousecanteen.com.au/</v>
+        <v>186</v>
       </c>
       <c r="J11" t="str">
-        <v>https://www.google.com/maps/place/Cubbyhouse+Canteen/@-37.8583368,145.0234773,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669dcf5747179:0xdf909f92969a2708!8m2!3d-37.8583368!4d145.0234773!16s%2Fg%2F12qgl7jmj?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$20–40</v>
       </c>
       <c r="K11" t="str">
-        <v>4.4</v>
+        <v>$20–40</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>42RF+H5 Armadale, Victoria, Australia</v>
       </c>
       <c r="M11" t="str">
-        <v>$1–20</v>
+        <v>https://www.google.com/maps/place/Pique+Nique/@-37.8586088,145.0228889,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669dc8a3b11fd:0x5c78c291e96d657!8m2!3d-37.8586088!4d145.0228889!16s%2Fg%2F1pzrk8chz?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N11" t="str">
-        <v>42RF+M9 Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Pique+Nique/data=!4m7!3m6!1s0x6ad669dc8a3b11fd:0x5c78c291e96d657!8m2!3d-37.8586088!4d145.0228889!16s%2Fg%2F1pzrk8chz!19sChIJ_RE7itxp1moRV9aWHimMxwU?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1030,10 +999,7 @@
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v>3/9/2026, 6:25:48 PM</v>
+        <v>3/9/2026, 6:44:14 PM</v>
       </c>
     </row>
     <row r="12">
@@ -1044,41 +1010,41 @@
         <v>Saki’s Coffee</v>
       </c>
       <c r="C12" t="str">
+        <v>+61 478 366 688</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1B Rose St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
         <v>4.6</v>
       </c>
-      <c r="D12" t="str">
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v>107</v>
       </c>
-      <c r="E12" t="str">
+      <c r="J12" t="str">
         <v>$1–20</v>
       </c>
-      <c r="F12" t="str">
+      <c r="K12" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="L12" t="str">
+        <v>42X7+MR Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M12" t="str">
+        <v>https://www.google.com/maps/place/Saki%E2%80%99s+Coffee/@-37.8507822,145.0145116,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6690f11b0c8c1:0xb507a9612c40a157!8m2!3d-37.8507822!4d145.0145116!16s%2Fg%2F11j4ksw4d1?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N12" t="str">
         <v>https://www.google.com/maps/place/Saki%E2%80%99s+Coffee/data=!4m7!3m6!1s0x6ad6690f11b0c8c1:0xb507a9612c40a157!8m2!3d-37.8507822!4d145.0145116!16s%2Fg%2F11j4ksw4d1!19sChIJwciwEQ9p1moRV6FALGGpB7U?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G12" t="str">
-        <v>1B Rose St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H12" t="str">
-        <v>+61 478 366 688</v>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v>https://www.google.com/maps/place/Saki%E2%80%99s+Coffee/@-37.8507822,145.0145116,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6690f11b0c8c1:0xb507a9612c40a157!8m2!3d-37.8507822!4d145.0145116!16s%2Fg%2F11j4ksw4d1?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K12" t="str">
-        <v>4.6</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v>$1–20</v>
-      </c>
-      <c r="N12" t="str">
-        <v>42X7+MR Armadale, Victoria, Australia</v>
-      </c>
       <c r="O12" t="str">
         <v/>
       </c>
@@ -1086,10 +1052,7 @@
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
-        <v>3/9/2026, 6:26:00 PM</v>
+        <v>3/9/2026, 6:44:26 PM</v>
       </c>
     </row>
     <row r="13">
@@ -1100,41 +1063,41 @@
         <v>Ned's Bake &amp; Bistro Armadale</v>
       </c>
       <c r="C13" t="str">
+        <v>+61 3 9824 4053</v>
+      </c>
+      <c r="D13" t="str">
+        <v>963 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E13" t="str">
+        <v>http://www.nedsbake.com.au/</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
         <v>4.3</v>
       </c>
-      <c r="D13" t="str">
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
         <v>168</v>
       </c>
-      <c r="E13" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="F13" t="str">
+      <c r="J13" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="K13" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="L13" t="str">
+        <v>42VC+V4 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M13" t="str">
+        <v>https://www.google.com/maps/place/Ned's+Bake+%26+Bistro+Armadale/@-37.855286,145.020309,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad66948027c88b1:0x7666dc368074c0e!8m2!3d-37.855286!4d145.020309!16s%2Fg%2F11rv37b_d2?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N13" t="str">
         <v>https://www.google.com/maps/place/Ned%27s+Bake+%26+Bistro+Armadale/data=!4m7!3m6!1s0x6ad66948027c88b1:0x7666dc368074c0e!8m2!3d-37.855286!4d145.020309!16s%2Fg%2F11rv37b_d2!19sChIJsYh8Akhp1moRDkwHaMNtZgc?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G13" t="str">
-        <v>963 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H13" t="str">
-        <v>+61 3 9824 4053</v>
-      </c>
-      <c r="I13" t="str">
-        <v>http://www.nedsbake.com.au/</v>
-      </c>
-      <c r="J13" t="str">
-        <v>https://www.google.com/maps/place/Ned's+Bake+%26+Bistro+Armadale/@-37.855286,145.020309,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad66948027c88b1:0x7666dc368074c0e!8m2!3d-37.855286!4d145.020309!16s%2Fg%2F11rv37b_d2?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K13" t="str">
-        <v>4.3</v>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="N13" t="str">
-        <v>42VC+V4 Armadale, Victoria, Australia</v>
-      </c>
       <c r="O13" t="str">
         <v/>
       </c>
@@ -1142,10 +1105,7 @@
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v/>
-      </c>
-      <c r="R13" t="str">
-        <v>3/9/2026, 6:26:11 PM</v>
+        <v>3/9/2026, 6:44:38 PM</v>
       </c>
     </row>
     <row r="14">
@@ -1156,41 +1116,41 @@
         <v>Hank's Bagelry - Armadale</v>
       </c>
       <c r="C14" t="str">
+        <v>+61 3 9125 1606</v>
+      </c>
+      <c r="D14" t="str">
+        <v>13 Beatty Ave, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E14" t="str">
+        <v>http://hanksbagelry.com.au/</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
         <v>4.6</v>
       </c>
-      <c r="D14" t="str">
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
         <v>205</v>
       </c>
-      <c r="E14" t="str">
+      <c r="J14" t="str">
         <v>$1–20</v>
       </c>
-      <c r="F14" t="str">
+      <c r="K14" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="L14" t="str">
+        <v>42X7+PP Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M14" t="str">
+        <v>https://www.google.com/maps/place/Hank's+Bagelry+-+Armadale/@-37.8507213,145.0142979,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6692801c6214b:0xd7e38ffd0d1d64e6!8m2!3d-37.8507213!4d145.0142979!16s%2Fg%2F11scg38mxg?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N14" t="str">
         <v>https://www.google.com/maps/place/Hank%27s+Bagelry+-+Armadale/data=!4m7!3m6!1s0x6ad6692801c6214b:0xd7e38ffd0d1d64e6!8m2!3d-37.8507213!4d145.0142979!16s%2Fg%2F11scg38mxg!19sChIJSyHGAShp1moR5mQdDf2P49c?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G14" t="str">
-        <v>13 Beatty Ave, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H14" t="str">
-        <v>+61 3 9125 1606</v>
-      </c>
-      <c r="I14" t="str">
-        <v>http://hanksbagelry.com.au/</v>
-      </c>
-      <c r="J14" t="str">
-        <v>https://www.google.com/maps/place/Hank's+Bagelry+-+Armadale/@-37.8507213,145.0142979,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6692801c6214b:0xd7e38ffd0d1d64e6!8m2!3d-37.8507213!4d145.0142979!16s%2Fg%2F11scg38mxg?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K14" t="str">
-        <v>4.6</v>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v>$1–20</v>
-      </c>
-      <c r="N14" t="str">
-        <v>42X7+PP Armadale, Victoria, Australia</v>
-      </c>
       <c r="O14" t="str">
         <v/>
       </c>
@@ -1198,10 +1158,7 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v/>
-      </c>
-      <c r="R14" t="str">
-        <v>3/9/2026, 6:26:24 PM</v>
+        <v>3/9/2026, 6:44:49 PM</v>
       </c>
     </row>
     <row r="15">
@@ -1212,52 +1169,49 @@
         <v>Lune Croissanterie Armadale</v>
       </c>
       <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>835 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E15" t="str">
+        <v>https://www.lunecroissanterie.com/</v>
+      </c>
+      <c r="F15" t="str">
+        <v>hello@lunecroissanterie.com</v>
+      </c>
+      <c r="G15" t="str">
         <v>4.3</v>
       </c>
-      <c r="D15" t="str">
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
         <v>481</v>
       </c>
-      <c r="E15" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="F15" t="str">
+      <c r="J15" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="K15" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="L15" t="str">
+        <v>42W8+45 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M15" t="str">
+        <v>https://www.google.com/maps/place/Lune+Croissanterie+Armadale/@-37.8546269,145.0153947,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6693f828b403b:0xdd00a2c9456a6862!8m2!3d-37.8546269!4d145.0153947!16s%2Fg%2F11s57f8t2l?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N15" t="str">
         <v>https://www.google.com/maps/place/Lune+Croissanterie+Armadale/data=!4m7!3m6!1s0x6ad6693f828b403b:0xdd00a2c9456a6862!8m2!3d-37.8546269!4d145.0153947!16s%2Fg%2F11s57f8t2l!19sChIJO0CLgj9p1moRYmhqRcmiAN0?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G15" t="str">
-        <v>835 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>https://www.lunecroissanterie.com/</v>
-      </c>
-      <c r="J15" t="str">
-        <v>https://www.google.com/maps/place/Lune+Croissanterie+Armadale/@-37.8546269,145.0153947,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6693f828b403b:0xdd00a2c9456a6862!8m2!3d-37.8546269!4d145.0153947!16s%2Fg%2F11s57f8t2l?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K15" t="str">
-        <v>4.3</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="N15" t="str">
-        <v>42W8+45 Armadale, Victoria, Australia</v>
-      </c>
       <c r="O15" t="str">
         <v/>
       </c>
       <c r="P15" t="str">
-        <v>hello@lunecroissanterie.com</v>
+        <v/>
       </c>
       <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v>3/9/2026, 6:26:33 PM</v>
+        <v>3/9/2026, 6:45:01 PM</v>
       </c>
     </row>
     <row r="16">
@@ -1268,41 +1222,41 @@
         <v>Euro Patisserie</v>
       </c>
       <c r="C16" t="str">
+        <v>+61 3 9509 5166</v>
+      </c>
+      <c r="D16" t="str">
+        <v>974 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E16" t="str">
+        <v>https://patisseries.com.au/</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
         <v>4.2</v>
       </c>
-      <c r="D16" t="str">
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
         <v>204</v>
       </c>
-      <c r="E16" t="str">
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
         <v>974 High St</v>
       </c>
-      <c r="F16" t="str">
+      <c r="L16" t="str">
+        <v>42VC+Q3 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M16" t="str">
+        <v>https://www.google.com/maps/place/Euro+Patisserie/@-37.8555027,145.0202229,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669dbde7cc6fb:0x3d7ede4e124dd153!8m2!3d-37.8555027!4d145.0202229!16s%2Fg%2F1tghpqv0?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N16" t="str">
         <v>https://www.google.com/maps/place/Euro+Patisserie/data=!4m7!3m6!1s0x6ad669dbde7cc6fb:0x3d7ede4e124dd153!8m2!3d-37.8555027!4d145.0202229!16s%2Fg%2F1tghpqv0!19sChIJ-8Z83ttp1moRU9FNEk7efj0?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G16" t="str">
-        <v>974 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H16" t="str">
-        <v>+61 3 9509 5166</v>
-      </c>
-      <c r="I16" t="str">
-        <v>https://patisseries.com.au/</v>
-      </c>
-      <c r="J16" t="str">
-        <v>https://www.google.com/maps/place/Euro+Patisserie/@-37.8555027,145.0202229,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669dbde7cc6fb:0x3d7ede4e124dd153!8m2!3d-37.8555027!4d145.0202229!16s%2Fg%2F1tghpqv0?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K16" t="str">
-        <v>4.2</v>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-      <c r="N16" t="str">
-        <v>42VC+Q3 Armadale, Victoria, Australia</v>
-      </c>
       <c r="O16" t="str">
         <v/>
       </c>
@@ -1310,10 +1264,7 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v/>
-      </c>
-      <c r="R16" t="str">
-        <v>3/9/2026, 6:26:45 PM</v>
+        <v>3/9/2026, 6:45:12 PM</v>
       </c>
     </row>
     <row r="17">
@@ -1324,41 +1275,41 @@
         <v>CALI JARDIN</v>
       </c>
       <c r="C17" t="str">
+        <v>+61 3 9191 0103</v>
+      </c>
+      <c r="D17" t="str">
+        <v>730 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E17" t="str">
+        <v>http://www.calijardin.com/</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
         <v>4.5</v>
       </c>
-      <c r="D17" t="str">
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
         <v>39</v>
       </c>
-      <c r="E17" t="str">
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
         <v>730 High St</v>
       </c>
-      <c r="F17" t="str">
+      <c r="L17" t="str">
+        <v>42W7+52 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M17" t="str">
+        <v>https://www.google.com/maps/place/CALI+JARDIN/@-37.8545691,145.0125345,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad66900127501e9:0x7dbed03707e7f043!8m2!3d-37.8545691!4d145.0125345!16s%2Fg%2F11lddj2y75?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N17" t="str">
         <v>https://www.google.com/maps/place/CALI+JARDIN/data=!4m7!3m6!1s0x6ad66900127501e9:0x7dbed03707e7f043!8m2!3d-37.8545691!4d145.0125345!16s%2Fg%2F11lddj2y75!19sChIJ6QF1EgBp1moRQ_DnBzfQvn0?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G17" t="str">
-        <v>730 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H17" t="str">
-        <v>+61 3 9191 0103</v>
-      </c>
-      <c r="I17" t="str">
-        <v>http://www.calijardin.com/</v>
-      </c>
-      <c r="J17" t="str">
-        <v>https://www.google.com/maps/place/CALI+JARDIN/@-37.8545691,145.0125345,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad66900127501e9:0x7dbed03707e7f043!8m2!3d-37.8545691!4d145.0125345!16s%2Fg%2F11lddj2y75?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K17" t="str">
-        <v>4.5</v>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-      <c r="N17" t="str">
-        <v>42W7+52 Armadale, Victoria, Australia</v>
-      </c>
       <c r="O17" t="str">
         <v/>
       </c>
@@ -1366,10 +1317,7 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v/>
-      </c>
-      <c r="R17" t="str">
-        <v>3/9/2026, 6:26:56 PM</v>
+        <v>3/9/2026, 6:45:25 PM</v>
       </c>
     </row>
     <row r="18">
@@ -1380,41 +1328,41 @@
         <v>Beatty and Rose Providore</v>
       </c>
       <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>Corner of Beatty Ave &amp;, 11 Beatty Ave, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
         <v>4.3</v>
       </c>
-      <c r="D18" t="str">
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
         <v>34</v>
       </c>
-      <c r="E18" t="str">
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
         <v>Corner of Beatty Ave &amp;, 11 Beatty Ave</v>
       </c>
-      <c r="F18" t="str">
+      <c r="L18" t="str">
+        <v>42X7+MP Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M18" t="str">
+        <v>https://www.google.com/maps/place/Beatty+and+Rose+Providore/@-37.8508003,145.0143543,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6693e5c3114cd:0x645b5b79eef55cad!8m2!3d-37.8508003!4d145.0143543!16s%2Fg%2F11fjvtp0ql?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N18" t="str">
         <v>https://www.google.com/maps/place/Beatty+and+Rose+Providore/data=!4m7!3m6!1s0x6ad6693e5c3114cd:0x645b5b79eef55cad!8m2!3d-37.8508003!4d145.0143543!16s%2Fg%2F11fjvtp0ql!19sChIJzRQxXD5p1moRrVz17nlbW2Q?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G18" t="str">
-        <v>Corner of Beatty Ave &amp;, 11 Beatty Ave, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v>https://www.google.com/maps/place/Beatty+and+Rose+Providore/@-37.8508003,145.0143543,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6693e5c3114cd:0x645b5b79eef55cad!8m2!3d-37.8508003!4d145.0143543!16s%2Fg%2F11fjvtp0ql?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K18" t="str">
-        <v>4.3</v>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-      <c r="N18" t="str">
-        <v>42X7+MP Armadale, Victoria, Australia</v>
-      </c>
       <c r="O18" t="str">
         <v/>
       </c>
@@ -1422,10 +1370,7 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v/>
-      </c>
-      <c r="R18" t="str">
-        <v>3/9/2026, 6:27:07 PM</v>
+        <v>3/9/2026, 6:45:35 PM</v>
       </c>
     </row>
     <row r="19">
@@ -1436,41 +1381,41 @@
         <v>Green Cup Armadale</v>
       </c>
       <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>1242 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E19" t="str">
+        <v>http://greencup.com.au/</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
         <v>4.1</v>
       </c>
-      <c r="D19" t="str">
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
         <v>196</v>
       </c>
-      <c r="E19" t="str">
+      <c r="J19" t="str">
         <v>$1–20</v>
       </c>
-      <c r="F19" t="str">
+      <c r="K19" t="str">
+        <v>$1–20</v>
+      </c>
+      <c r="L19" t="str">
+        <v>42VH+86 Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M19" t="str">
+        <v>https://www.google.com/maps/place/Green+Cup+Armadale/@-37.856667,145.02812,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669e097a5d7c3:0x13bca0446945e07f!8m2!3d-37.856667!4d145.02812!16s%2Fg%2F11ckvynh41?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N19" t="str">
         <v>https://www.google.com/maps/place/Green+Cup+Armadale/data=!4m7!3m6!1s0x6ad669e097a5d7c3:0x13bca0446945e07f!8m2!3d-37.856667!4d145.02812!16s%2Fg%2F11ckvynh41!19sChIJw9ell-Bp1moRf-BFaUSgvBM?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G19" t="str">
-        <v>1242 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v>http://greencup.com.au/</v>
-      </c>
-      <c r="J19" t="str">
-        <v>https://www.google.com/maps/place/Green+Cup+Armadale/@-37.856667,145.02812,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669e097a5d7c3:0x13bca0446945e07f!8m2!3d-37.856667!4d145.02812!16s%2Fg%2F11ckvynh41?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K19" t="str">
-        <v>4.1</v>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v>$1–20</v>
-      </c>
-      <c r="N19" t="str">
-        <v>42VH+86 Armadale, Victoria, Australia</v>
-      </c>
       <c r="O19" t="str">
         <v/>
       </c>
@@ -1478,10 +1423,7 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v/>
-      </c>
-      <c r="R19" t="str">
-        <v>3/9/2026, 6:27:19 PM</v>
+        <v>3/9/2026, 6:45:44 PM</v>
       </c>
     </row>
     <row r="20">
@@ -1492,40 +1434,40 @@
         <v>8days Cafe</v>
       </c>
       <c r="C20" t="str">
+        <v>+61 3 7013 3922</v>
+      </c>
+      <c r="D20" t="str">
+        <v>1184 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E20" t="str">
+        <v>https://www.8dayscafe.com.au/</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
         <v>4.1</v>
       </c>
-      <c r="D20" t="str">
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
         <v>330</v>
       </c>
-      <c r="E20" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="F20" t="str">
+      <c r="J20" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="K20" t="str">
+        <v>$20–40</v>
+      </c>
+      <c r="L20" t="str">
+        <v>42VG+CP Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M20" t="str">
+        <v>https://www.google.com/maps/place/8days+Cafe/@-37.8564094,145.0267625,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de2212a9ab:0x6230683dbec306fa!8m2!3d-37.8564094!4d145.0267625!16s%2Fg%2F1tqnls8j?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N20" t="str">
         <v>https://www.google.com/maps/place/8days+Cafe/data=!4m7!3m6!1s0x6ad669de2212a9ab:0x6230683dbec306fa!8m2!3d-37.8564094!4d145.0267625!16s%2Fg%2F1tqnls8j!19sChIJq6kSIt5p1moR-gbDvj1oMGI?authuser=0&amp;hl=en&amp;rclk=1</v>
-      </c>
-      <c r="G20" t="str">
-        <v>1184 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H20" t="str">
-        <v>+61 3 7013 3922</v>
-      </c>
-      <c r="I20" t="str">
-        <v>https://www.8dayscafe.com.au/</v>
-      </c>
-      <c r="J20" t="str">
-        <v>https://www.google.com/maps/place/8days+Cafe/@-37.8564094,145.0267625,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de2212a9ab:0x6230683dbec306fa!8m2!3d-37.8564094!4d145.0267625!16s%2Fg%2F1tqnls8j?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K20" t="str">
-        <v>4.1</v>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="N20" t="str">
-        <v>42VG+CP Armadale, Victoria, Australia</v>
       </c>
       <c r="O20" t="str">
         <v>Bustling, stylish cafe whipping up coffee &amp; espresso drinks, plus global breakfast &amp; lunch fare.</v>
@@ -1534,10 +1476,7 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v/>
-      </c>
-      <c r="R20" t="str">
-        <v>3/9/2026, 6:27:29 PM</v>
+        <v>3/9/2026, 6:45:54 PM</v>
       </c>
     </row>
     <row r="21">
@@ -1545,43 +1484,43 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>The Cake Club.</v>
+        <v>Cafe Claremont</v>
       </c>
       <c r="C21" t="str">
-        <v>4.9</v>
+        <v>+61 3 9500 1504</v>
       </c>
       <c r="D21" t="str">
-        <v>127</v>
+        <v>5 Claremont Ave, Malvern VIC 3144, Australia</v>
       </c>
       <c r="E21" t="str">
-        <v>$1–20</v>
+        <v>http://www.cafeclaremont.net.au/</v>
       </c>
       <c r="F21" t="str">
-        <v>https://www.google.com/maps/place/The+Cake+Club./data=!4m7!3m6!1s0x6ad66997e1cedd23:0xbbd2fa7b7159f859!8m2!3d-37.8545586!4d145.0121688!16s%2Fg%2F11kq43f6kl!19sChIJI93O4Zdp1moRWfhZcXv60rs?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>722 High St, Armadale VIC 3143, Australia</v>
+        <v>4.5</v>
       </c>
       <c r="H21" t="str">
-        <v>+61 483 794 616</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>http://thecakeclub.co/</v>
+        <v>305</v>
       </c>
       <c r="J21" t="str">
-        <v>https://www.google.com/maps/place/The+Cake+Club./@-37.8545586,145.0121688,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad66997e1cedd23:0xbbd2fa7b7159f859!8m2!3d-37.8545586!4d145.0121688!16s%2Fg%2F11kq43f6kl?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$20–40</v>
       </c>
       <c r="K21" t="str">
-        <v>4.9</v>
+        <v>$20–40</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>42MH+PV Malvern, Victoria, Australia</v>
       </c>
       <c r="M21" t="str">
-        <v>$1–20</v>
+        <v>https://www.google.com/maps/place/Cafe+Claremont/@-37.8657276,145.0296768,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669e9ac7571ef:0x47aec43ac3e3d6b8!8m2!3d-37.8657276!4d145.0296768!16s%2Fg%2F1v5k34nc?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N21" t="str">
-        <v>42W6+5V Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Cafe+Claremont/data=!4m7!3m6!1s0x6ad669e9ac7571ef:0x47aec43ac3e3d6b8!8m2!3d-37.8657276!4d145.0296768!16s%2Fg%2F1v5k34nc!19sChIJ73F1rOlp1moRuNbjwzrErkc?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -1590,10 +1529,7 @@
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v/>
-      </c>
-      <c r="R21" t="str">
-        <v>3/9/2026, 6:27:41 PM</v>
+        <v>3/9/2026, 6:46:06 PM</v>
       </c>
     </row>
     <row r="22">
@@ -1601,43 +1537,43 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Auterra Wine Bar</v>
+        <v>Prickly Pear</v>
       </c>
       <c r="C22" t="str">
-        <v>4.7</v>
+        <v>+61 3 9509 3910</v>
       </c>
       <c r="D22" t="str">
-        <v>215</v>
+        <v>75 Glenferrie Rd, Malvern VIC 3144, Australia</v>
       </c>
       <c r="E22" t="str">
-        <v></v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>https://www.google.com/maps/place/Auterra+Wine+Bar/data=!4m7!3m6!1s0x6ad669184a3fe71b:0x21cd4a01c45abfcd!8m2!3d-37.8562794!4d145.02602!16s%2Fg%2F11nfsyk0ks!19sChIJG-c_Shhp1moRzb9axAFKzSE?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>1160 High St, Armadale VIC 3143, Australia</v>
+        <v>4.4</v>
       </c>
       <c r="H22" t="str">
-        <v>+61 3 8529 2660</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>http://auterrawinebar.com.au/</v>
+        <v>202</v>
       </c>
       <c r="J22" t="str">
-        <v>https://www.google.com/maps/place/Auterra+Wine+Bar/@-37.8562794,145.02602,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669184a3fe71b:0x21cd4a01c45abfcd!8m2!3d-37.8562794!4d145.02602!16s%2Fg%2F11nfsyk0ks?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$1–20</v>
       </c>
       <c r="K22" t="str">
-        <v>4.7</v>
+        <v>$1–20</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>42PH+Q5 Malvern, Victoria, Australia</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>https://www.google.com/maps/place/Prickly+Pear/@-37.8630676,145.0279907,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669e80f0dc7f1:0x4c9662f64975953e!8m2!3d-37.8630676!4d145.0279907!16s%2Fg%2F1pwfxh846?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N22" t="str">
-        <v>42VG+FC Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Prickly+Pear/data=!4m7!3m6!1s0x6ad669e80f0dc7f1:0x4c9662f64975953e!8m2!3d-37.8630676!4d145.0279907!16s%2Fg%2F1pwfxh846!19sChIJ8ccND-hp1moRPpV1SfZilkw?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -1646,10 +1582,7 @@
         <v/>
       </c>
       <c r="Q22" t="str">
-        <v/>
-      </c>
-      <c r="R22" t="str">
-        <v>3/9/2026, 6:27:52 PM</v>
+        <v>3/9/2026, 6:46:19 PM</v>
       </c>
     </row>
     <row r="23">
@@ -1657,43 +1590,43 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Pony</v>
+        <v>The Cake Club.</v>
       </c>
       <c r="C23" t="str">
-        <v>4.8</v>
+        <v>+61 483 794 616</v>
       </c>
       <c r="D23" t="str">
-        <v>151</v>
+        <v>722 High St, Armadale VIC 3143, Australia</v>
       </c>
       <c r="E23" t="str">
-        <v>14 Beatty Ave</v>
+        <v>http://thecakeclub.co/</v>
       </c>
       <c r="F23" t="str">
-        <v>https://www.google.com/maps/place/Pony/data=!4m7!3m6!1s0x6ad6699d6a445fef:0xe24e098d37e6d080!8m2!3d-37.8506722!4d145.0142614!16s%2Fg%2F11vc86kknr!19sChIJ719Eap1p1moRgNDmN40JTuI?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>14 Beatty Ave, Armadale VIC 3143, Australia</v>
+        <v>4.9</v>
       </c>
       <c r="H23" t="str">
-        <v>+61 3 9326 2162</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>http://pony.melbourne/</v>
+        <v>127</v>
       </c>
       <c r="J23" t="str">
-        <v>https://www.google.com/maps/place/Pony/@-37.8506722,145.0142614,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6699d6a445fef:0xe24e098d37e6d080!8m2!3d-37.8506722!4d145.0142614!16s%2Fg%2F11vc86kknr?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$1–20</v>
       </c>
       <c r="K23" t="str">
-        <v>4.8</v>
+        <v>$1–20</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>42W6+5V Armadale, Victoria, Australia</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>https://www.google.com/maps/place/The+Cake+Club./@-37.8545586,145.0121688,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad66997e1cedd23:0xbbd2fa7b7159f859!8m2!3d-37.8545586!4d145.0121688!16s%2Fg%2F11kq43f6kl?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N23" t="str">
-        <v>42X7+PP Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/The+Cake+Club./data=!4m7!3m6!1s0x6ad66997e1cedd23:0xbbd2fa7b7159f859!8m2!3d-37.8545586!4d145.0121688!16s%2Fg%2F11kq43f6kl!19sChIJI93O4Zdp1moRWfhZcXv60rs?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1702,10 +1635,7 @@
         <v/>
       </c>
       <c r="Q23" t="str">
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <v>3/9/2026, 6:28:04 PM</v>
+        <v>3/9/2026, 6:46:29 PM</v>
       </c>
     </row>
     <row r="24">
@@ -1716,41 +1646,41 @@
         <v>Zia Rina's Cucina</v>
       </c>
       <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>857 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E24" t="str">
+        <v>http://www.rinas3143.com/</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
         <v>4.6</v>
       </c>
-      <c r="D24" t="str">
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
         <v>197</v>
       </c>
-      <c r="E24" t="str">
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
         <v>857 High St</v>
       </c>
-      <c r="F24" t="str">
+      <c r="L24" t="str">
+        <v>42W8+4C Armadale, Victoria, Australia</v>
+      </c>
+      <c r="M24" t="str">
+        <v>https://www.google.com/maps/place/Zia+Rina's+Cucina/@-37.854664,145.016019,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d0a6f28359:0x6c98c51433efa1fa!8m2!3d-37.854664!4d145.016019!16s%2Fg%2F1hc2x6jgg?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+      </c>
+      <c r="N24" t="str">
         <v>https://www.google.com/maps/place/Zia+Rina%27s+Cucina/data=!4m7!3m6!1s0x6ad669d0a6f28359:0x6c98c51433efa1fa!8m2!3d-37.854664!4d145.016019!16s%2Fg%2F1hc2x6jgg!19sChIJWYPyptBp1moR-qHvMxTFmGw?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
-      <c r="G24" t="str">
-        <v>857 High St, Armadale VIC 3143, Australia</v>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v>http://www.rinas3143.com/</v>
-      </c>
-      <c r="J24" t="str">
-        <v>https://www.google.com/maps/place/Zia+Rina's+Cucina/@-37.854664,145.016019,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d0a6f28359:0x6c98c51433efa1fa!8m2!3d-37.854664!4d145.016019!16s%2Fg%2F1hc2x6jgg?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
-      </c>
-      <c r="K24" t="str">
-        <v>4.6</v>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v>42W8+4C Armadale, Victoria, Australia</v>
-      </c>
       <c r="O24" t="str">
         <v/>
       </c>
@@ -1758,10 +1688,7 @@
         <v/>
       </c>
       <c r="Q24" t="str">
-        <v/>
-      </c>
-      <c r="R24" t="str">
-        <v>3/9/2026, 6:28:16 PM</v>
+        <v>3/9/2026, 6:46:40 PM</v>
       </c>
     </row>
     <row r="25">
@@ -1769,43 +1696,43 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Jack's House Cafe</v>
+        <v>The Green Goose</v>
       </c>
       <c r="C25" t="str">
-        <v>4.6</v>
+        <v>+61 3 9576 0044</v>
       </c>
       <c r="D25" t="str">
-        <v>153</v>
+        <v>9 Station St, Malvern VIC 3144, Australia</v>
       </c>
       <c r="E25" t="str">
-        <v>$20–40</v>
+        <v>http://thegreengoose.com.au/</v>
       </c>
       <c r="F25" t="str">
-        <v>https://www.google.com/maps/place/Jack%27s+House+Cafe/data=!4m7!3m6!1s0x6ad669fd4213e46f:0xac9c9b2bf55099a7!8m2!3d-37.8580501!4d145.0396302!16s%2Fg%2F11g0g2b711!19sChIJb-QTQv1p1moRp5lQ9SubnKw?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>1398 High St, Malvern VIC 3144, Australia</v>
+        <v>4.5</v>
       </c>
       <c r="H25" t="str">
-        <v>+61 405 169 055</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>189</v>
       </c>
       <c r="J25" t="str">
-        <v>https://www.google.com/maps/place/Jack's+House+Cafe/@-37.8580501,145.0396302,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669fd4213e46f:0xac9c9b2bf55099a7!8m2!3d-37.8580501!4d145.0396302!16s%2Fg%2F11g0g2b711?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$1–20</v>
       </c>
       <c r="K25" t="str">
-        <v>4.6</v>
+        <v>$1–20</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>42PH+39 Malvern, Victoria, Australia</v>
       </c>
       <c r="M25" t="str">
-        <v>$20–40</v>
+        <v>https://www.google.com/maps/place/The+Green+Goose/@-37.8647919,145.0283764,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669e831bbf865:0x47c0e6df2fbb4aba!8m2!3d-37.8647919!4d145.0283764!16s%2Fg%2F1tx_6hns?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N25" t="str">
-        <v>42RQ+QV Malvern, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/The+Green+Goose/data=!4m7!3m6!1s0x6ad669e831bbf865:0x47c0e6df2fbb4aba!8m2!3d-37.8647919!4d145.0283764!16s%2Fg%2F1tx_6hns!19sChIJZfi7Mehp1moRukq7L9_mwEc?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -1814,10 +1741,7 @@
         <v/>
       </c>
       <c r="Q25" t="str">
-        <v/>
-      </c>
-      <c r="R25" t="str">
-        <v>3/9/2026, 6:28:25 PM</v>
+        <v>3/9/2026, 6:46:51 PM</v>
       </c>
     </row>
     <row r="26">
@@ -1825,55 +1749,52 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Bouzy Bar Armadale</v>
+        <v>La Dolce Vita Pizza Bar</v>
       </c>
       <c r="C26" t="str">
-        <v>4.6</v>
+        <v>+61 423 316 665</v>
       </c>
       <c r="D26" t="str">
-        <v>81</v>
+        <v>708 High St, Armadale VIC 3143, Australia</v>
       </c>
       <c r="E26" t="str">
-        <v>976 High St</v>
+        <v/>
       </c>
       <c r="F26" t="str">
-        <v>https://www.google.com/maps/place/Bouzy+Bar+Armadale/data=!4m7!3m6!1s0x6ad6695501d31029:0x8a5205e762ad2ea3!8m2!3d-37.8556142!4d145.0203607!16s%2Fg%2F11y623dph3!19sChIJKRDTAVVp1moRoy6tYucFUoo?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>976 High St, Armadale VIC 3143, Australia</v>
+        <v>4.7</v>
       </c>
       <c r="H26" t="str">
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>https://www.bouzy.au/</v>
+        <v>76</v>
       </c>
       <c r="J26" t="str">
-        <v>https://www.google.com/maps/place/Bouzy+Bar+Armadale/@-37.8556142,145.0203607,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6695501d31029:0x8a5205e762ad2ea3!8m2!3d-37.8556142!4d145.0203607!16s%2Fg%2F11y623dph3?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$20–40</v>
       </c>
       <c r="K26" t="str">
-        <v>4.6</v>
+        <v>$20–40</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>42W6+6M Armadale, Victoria, Australia</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>https://www.google.com/maps/place/La+Dolce+Vita+Pizza+Bar/@-37.854484,145.011738,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d176bcf111:0xc634fcb48386270e!8m2!3d-37.854484!4d145.011738!16s%2Fg%2F1tdzg3zt?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N26" t="str">
-        <v>42VC+Q4 Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/La+Dolce+Vita+Pizza+Bar/data=!4m7!3m6!1s0x6ad669d176bcf111:0xc634fcb48386270e!8m2!3d-37.854484!4d145.011738!16s%2Fg%2F1tdzg3zt!19sChIJEfG8dtFp1moRDieGg7T8NMY?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O26" t="str">
-        <v/>
+        <v>Typical Italian toppings, plus creative flavours, in a snug, unassuming pizzeria with simple decor.</v>
       </c>
       <c r="P26" t="str">
         <v/>
       </c>
       <c r="Q26" t="str">
-        <v/>
-      </c>
-      <c r="R26" t="str">
-        <v>3/9/2026, 6:28:35 PM</v>
+        <v>3/9/2026, 6:47:04 PM</v>
       </c>
     </row>
     <row r="27">
@@ -1881,43 +1802,43 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>Amaru</v>
+        <v>Auterra Wine Bar</v>
       </c>
       <c r="C27" t="str">
+        <v>+61 3 8529 2660</v>
+      </c>
+      <c r="D27" t="str">
+        <v>1160 High St, Armadale VIC 3143, Australia</v>
+      </c>
+      <c r="E27" t="str">
+        <v>http://auterrawinebar.com.au/</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
         <v>4.7</v>
       </c>
-      <c r="D27" t="str">
-        <v>522</v>
-      </c>
-      <c r="E27" t="str">
-        <v>$200+</v>
-      </c>
-      <c r="F27" t="str">
-        <v>https://www.google.com/maps/place/Amaru/data=!4m7!3m6!1s0x6ad669de5e639241:0xe32e752ff825edf1!8m2!3d-37.8558133!4d145.0249461!16s%2Fg%2F11cjp_p_hl!19sChIJQZJjXt5p1moR8e0l-C91LuM?authuser=0&amp;hl=en&amp;rclk=1</v>
-      </c>
-      <c r="G27" t="str">
-        <v>1121 High St, Armadale VIC 3143, Australia</v>
-      </c>
       <c r="H27" t="str">
-        <v>+61 420 391 732</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v>http://amarumelbourne.com.au/</v>
+        <v>215</v>
       </c>
       <c r="J27" t="str">
-        <v>https://www.google.com/maps/place/Amaru/@-37.8558133,145.0249461,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669de5e639241:0xe32e752ff825edf1!8m2!3d-37.8558133!4d145.0249461!16s%2Fg%2F11cjp_p_hl?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v/>
       </c>
       <c r="K27" t="str">
-        <v>4.7</v>
+        <v></v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>42VG+FC Armadale, Victoria, Australia</v>
       </c>
       <c r="M27" t="str">
-        <v>$200+</v>
+        <v>https://www.google.com/maps/place/Auterra+Wine+Bar/@-37.8562794,145.02602,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669184a3fe71b:0x21cd4a01c45abfcd!8m2!3d-37.8562794!4d145.02602!16s%2Fg%2F11nfsyk0ks?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N27" t="str">
-        <v>42VF+MX Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Auterra+Wine+Bar/data=!4m7!3m6!1s0x6ad669184a3fe71b:0x21cd4a01c45abfcd!8m2!3d-37.8562794!4d145.02602!16s%2Fg%2F11nfsyk0ks!19sChIJG-c_Shhp1moRzb9axAFKzSE?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O27" t="str">
         <v/>
@@ -1926,10 +1847,7 @@
         <v/>
       </c>
       <c r="Q27" t="str">
-        <v/>
-      </c>
-      <c r="R27" t="str">
-        <v>3/9/2026, 6:28:45 PM</v>
+        <v>3/9/2026, 6:47:16 PM</v>
       </c>
     </row>
     <row r="28">
@@ -1937,55 +1855,52 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Cafe Latte</v>
+        <v>Thirty Mill</v>
       </c>
       <c r="C28" t="str">
+        <v>+61 3 9804 3653</v>
+      </c>
+      <c r="D28" t="str">
+        <v>66 Milton Parade, Malvern VIC 3144, Australia</v>
+      </c>
+      <c r="E28" t="str">
+        <v>https://www.thirtymill.com/</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
         <v>4.5</v>
       </c>
-      <c r="D28" t="str">
-        <v>284</v>
-      </c>
-      <c r="E28" t="str">
-        <v>$20–40</v>
-      </c>
-      <c r="F28" t="str">
-        <v>https://www.google.com/maps/place/Cafe+Latte/data=!4m7!3m6!1s0x6ad6682b17e1b84b:0x8494ab429665d4d0!8m2!3d-37.8480169!4d145.0038932!16s%2Fg%2F1tls2zw_!19sChIJS7jhFyto1moR0NRllkKrlIQ?authuser=0&amp;hl=en&amp;rclk=1</v>
-      </c>
-      <c r="G28" t="str">
-        <v>521 Malvern Rd, Toorak VIC 3142, Australia</v>
-      </c>
       <c r="H28" t="str">
-        <v>+61 3 7036 0084</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>https://www.cafelattehawksburn.com/</v>
+        <v>362</v>
       </c>
       <c r="J28" t="str">
-        <v>https://www.google.com/maps/place/Cafe+Latte/@-37.8480169,145.0038932,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6682b17e1b84b:0x8494ab429665d4d0!8m2!3d-37.8480169!4d145.0038932!16s%2Fg%2F1tls2zw_?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$20–40</v>
       </c>
       <c r="K28" t="str">
-        <v>4.5</v>
+        <v>$20–40</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>522R+79 Malvern, Victoria, Australia</v>
       </c>
       <c r="M28" t="str">
-        <v>$20–40</v>
+        <v>https://www.google.com/maps/place/Thirty+Mill/@-37.8493455,145.0408918,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6420520e26267:0x557c61df6741dc78!8m2!3d-37.8493455!4d145.0408918!16s%2Fg%2F1tgmwf0n?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N28" t="str">
-        <v>5223+QH Toorak, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Thirty+Mill/data=!4m7!3m6!1s0x6ad6420520e26267:0x557c61df6741dc78!8m2!3d-37.8493455!4d145.0408918!16s%2Fg%2F1tgmwf0n!19sChIJZ2LiIAVC1moReNxBZ99hfFU?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O28" t="str">
-        <v>Modern cafe offering breakfast, lunch &amp; brunch, plus  a variety of coffee drinks.</v>
+        <v/>
       </c>
       <c r="P28" t="str">
         <v/>
       </c>
       <c r="Q28" t="str">
-        <v/>
-      </c>
-      <c r="R28" t="str">
-        <v>3/9/2026, 6:28:57 PM</v>
+        <v>3/9/2026, 6:47:25 PM</v>
       </c>
     </row>
     <row r="29">
@@ -1993,43 +1908,43 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Victor Churchill</v>
+        <v>TONIC &amp; GRACE</v>
       </c>
       <c r="C29" t="str">
-        <v>4.7</v>
+        <v>+61 3 8590 3121</v>
       </c>
       <c r="D29" t="str">
-        <v>695</v>
+        <v>63 Glenferrie Rd, Malvern VIC 3144, Australia</v>
       </c>
       <c r="E29" t="str">
-        <v></v>
+        <v>https://tonicandgrace.com.au/</v>
       </c>
       <c r="F29" t="str">
-        <v>https://www.google.com/maps/place/Victor+Churchill/data=!4m7!3m6!1s0x6ad669f5c4a83fed:0x54037a72852158f7!8m2!3d-37.8552206!4d145.020079!16s%2Fg%2F11pc9nmtsn!19sChIJ7T-oxPVp1moR91ghhXJ6A1Q?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v>953 High St, Armadale VIC 3143, Australia</v>
+        <v>4.6</v>
       </c>
       <c r="H29" t="str">
-        <v>+61 3 9978 1968</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v>https://victorchurchill.com/pages/melbourne/?utm_source=google+my+business&amp;utm_medium=organic</v>
+        <v>316</v>
       </c>
       <c r="J29" t="str">
-        <v>https://www.google.com/maps/place/Victor+Churchill/@-37.8552206,145.020079,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669f5c4a83fed:0x54037a72852158f7!8m2!3d-37.8552206!4d145.020079!16s%2Fg%2F11pc9nmtsn?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$20–40</v>
       </c>
       <c r="K29" t="str">
-        <v>4.7</v>
+        <v>$20–40</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>42PH+M5 Malvern, Victoria, Australia</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>https://www.google.com/maps/place/TONIC+%26+GRACE/@-37.863341,145.027979,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669e8107f4097:0x14d37bf4f47c7a9!8m2!3d-37.863341!4d145.027979!16s%2Fg%2F11hbg9l501?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N29" t="str">
-        <v>42VC+W2 Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/TONIC+%26+GRACE/data=!4m7!3m6!1s0x6ad669e8107f4097:0x14d37bf4f47c7a9!8m2!3d-37.863341!4d145.027979!16s%2Fg%2F11hbg9l501!19sChIJl0B_EOhp1moRqcdHT783TQE?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O29" t="str">
         <v/>
@@ -2038,10 +1953,7 @@
         <v/>
       </c>
       <c r="Q29" t="str">
-        <v/>
-      </c>
-      <c r="R29" t="str">
-        <v>3/9/2026, 6:29:08 PM</v>
+        <v>3/9/2026, 6:47:35 PM</v>
       </c>
     </row>
     <row r="30">
@@ -2049,43 +1961,43 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Thirty Mill</v>
+        <v>Pony</v>
       </c>
       <c r="C30" t="str">
-        <v>4.5</v>
+        <v>+61 3 9326 2162</v>
       </c>
       <c r="D30" t="str">
-        <v>362</v>
+        <v>14 Beatty Ave, Armadale VIC 3143, Australia</v>
       </c>
       <c r="E30" t="str">
-        <v>$20–40</v>
+        <v>http://pony.melbourne/</v>
       </c>
       <c r="F30" t="str">
-        <v>https://www.google.com/maps/place/Thirty+Mill/data=!4m7!3m6!1s0x6ad6420520e26267:0x557c61df6741dc78!8m2!3d-37.8493455!4d145.0408918!16s%2Fg%2F1tgmwf0n!19sChIJZ2LiIAVC1moReNxBZ99hfFU?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G30" t="str">
-        <v>66 Milton Parade, Malvern VIC 3144, Australia</v>
+        <v>4.8</v>
       </c>
       <c r="H30" t="str">
-        <v>+61 3 9804 3653</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v>https://www.thirtymill.com/</v>
+        <v>151</v>
       </c>
       <c r="J30" t="str">
-        <v>https://www.google.com/maps/place/Thirty+Mill/@-37.8493455,145.0408918,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6420520e26267:0x557c61df6741dc78!8m2!3d-37.8493455!4d145.0408918!16s%2Fg%2F1tgmwf0n?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v/>
       </c>
       <c r="K30" t="str">
-        <v>4.5</v>
+        <v>14 Beatty Ave</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>42X7+PP Armadale, Victoria, Australia</v>
       </c>
       <c r="M30" t="str">
-        <v>$20–40</v>
+        <v>https://www.google.com/maps/place/Pony/@-37.8506722,145.0142614,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6699d6a445fef:0xe24e098d37e6d080!8m2!3d-37.8506722!4d145.0142614!16s%2Fg%2F11vc86kknr?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N30" t="str">
-        <v>522R+79 Malvern, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Pony/data=!4m7!3m6!1s0x6ad6699d6a445fef:0xe24e098d37e6d080!8m2!3d-37.8506722!4d145.0142614!16s%2Fg%2F11vc86kknr!19sChIJ719Eap1p1moRgNDmN40JTuI?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O30" t="str">
         <v/>
@@ -2094,10 +2006,7 @@
         <v/>
       </c>
       <c r="Q30" t="str">
-        <v/>
-      </c>
-      <c r="R30" t="str">
-        <v>3/9/2026, 6:29:20 PM</v>
+        <v>3/9/2026, 6:47:48 PM</v>
       </c>
     </row>
     <row r="31">
@@ -2105,67 +2014,68 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Phillippa's Bakery</v>
+        <v>Cafe Latte</v>
       </c>
       <c r="C31" t="str">
-        <v>4.0</v>
+        <v>+61 3 7036 0084</v>
       </c>
       <c r="D31" t="str">
-        <v>158</v>
+        <v>521 Malvern Rd, Toorak VIC 3142, Australia</v>
       </c>
       <c r="E31" t="str">
-        <v>$1–20</v>
+        <v>https://www.cafelattehawksburn.com/</v>
       </c>
       <c r="F31" t="str">
-        <v>https://www.google.com/maps/place/Phillippa%27s+Bakery/data=!4m7!3m6!1s0x6ad669d9550dd479:0xf2ae5dae0da13b22!8m2!3d-37.8557517!4d145.021603!16s%2Fg%2F1v2jd1dn!19sChIJedQNVdlp1moRIjuhDa5drvI?authuser=0&amp;hl=en&amp;rclk=1</v>
+        <v/>
       </c>
       <c r="G31" t="str">
-        <v>1030 High St, Armadale VIC 3143, Australia</v>
+        <v>4.5</v>
       </c>
       <c r="H31" t="str">
-        <v>+61 3 9576 2020</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v>http://www.phillippas.com.au/</v>
+        <v>284</v>
       </c>
       <c r="J31" t="str">
-        <v>https://www.google.com/maps/place/Phillippa's+Bakery/@-37.8557517,145.021603,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad669d9550dd479:0xf2ae5dae0da13b22!8m2!3d-37.8557517!4d145.021603!16s%2Fg%2F1v2jd1dn?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
+        <v>$20–40</v>
       </c>
       <c r="K31" t="str">
-        <v>4.0</v>
+        <v>$20–40</v>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>5223+QH Toorak, Victoria, Australia</v>
       </c>
       <c r="M31" t="str">
-        <v>$1–20</v>
+        <v>https://www.google.com/maps/place/Cafe+Latte/@-37.8480169,145.0038932,17z/data=!3m1!4b1!4m6!3m5!1s0x6ad6682b17e1b84b:0x8494ab429665d4d0!8m2!3d-37.8480169!4d145.0038932!16s%2Fg%2F1tls2zw_?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMwNC4xIKXMDSoASAFQAw%3D%3D</v>
       </c>
       <c r="N31" t="str">
-        <v>42VC+MJ Armadale, Victoria, Australia</v>
+        <v>https://www.google.com/maps/place/Cafe+Latte/data=!4m7!3m6!1s0x6ad6682b17e1b84b:0x8494ab429665d4d0!8m2!3d-37.8480169!4d145.0038932!16s%2Fg%2F1tls2zw_!19sChIJS7jhFyto1moR0NRllkKrlIQ?authuser=0&amp;hl=en&amp;rclk=1</v>
       </c>
       <c r="O31" t="str">
-        <v/>
+        <v>Modern cafe offering breakfast, lunch &amp; brunch, plus  a variety of coffee drinks.</v>
       </c>
       <c r="P31" t="str">
         <v/>
       </c>
       <c r="Q31" t="str">
-        <v/>
-      </c>
-      <c r="R31" t="str">
-        <v>3/9/2026, 6:29:31 PM</v>
+        <v>3/9/2026, 6:47:58 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2217,18 +2127,18 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Businesses with Address</v>
+        <v>Businesses with Phone</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Businesses with Phone</v>
+        <v>Businesses with Address</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -2236,7 +2146,7 @@
         <v>Businesses with Website</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -2252,44 +2162,44 @@
         <v>Businesses with Hours</v>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v/>
+        <v>Businesses with Rating</v>
+      </c>
+      <c r="B12">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Extraction Date</v>
+        <v/>
       </c>
       <c r="B13" t="str">
-        <v>3/9/2026, 6:29:31 PM</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Data Sheet</v>
+        <v>Extraction Date</v>
       </c>
       <c r="B14" t="str">
-        <v>Businesses</v>
+        <v>3/9/2026, 6:47:58 PM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Data Sheet</v>
       </c>
       <c r="B15" t="str">
-        <v/>
+        <v>Businesses</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Rating Statistics</v>
+        <v/>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -2297,31 +2207,39 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Average Rating</v>
+        <v>Rating Statistics</v>
       </c>
       <c r="B17" t="str">
-        <v>4.46</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Highest Rating</v>
+        <v>Average Rating</v>
       </c>
       <c r="B18" t="str">
-        <v>4.9</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>Highest Rating</v>
+      </c>
+      <c r="B19" t="str">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>Lowest Rating</v>
       </c>
-      <c r="B19" t="str">
-        <v>4.0</v>
+      <c r="B20" t="str">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B20"/>
   </ignoredErrors>
 </worksheet>
 </file>